--- a/prairies/data/Releves_prairies_biomasse_et_phyto.xlsx
+++ b/prairies/data/Releves_prairies_biomasse_et_phyto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ingé\3A\Stage\Cervides_Aubrac\Analyse\Analyses_Aubrac\prairies\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDB1320-7495-4B65-9E6C-E30627F76C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08129C2C-6BF2-4EFA-8459-527617A30ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISEZ-MOI" sheetId="13" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="477">
   <si>
     <t>Id_EE</t>
   </si>
@@ -242,9 +242,6 @@
     <t>AUGUY Francis</t>
   </si>
   <si>
-    <t xml:space="preserve">Bessière </t>
-  </si>
-  <si>
     <t>annee</t>
   </si>
   <si>
@@ -542,9 +539,6 @@
     <t>P12</t>
   </si>
   <si>
-    <t>P13A</t>
-  </si>
-  <si>
     <t>P13B</t>
   </si>
   <si>
@@ -581,9 +575,6 @@
     <t>P19</t>
   </si>
   <si>
-    <t>P20A</t>
-  </si>
-  <si>
     <t>P21</t>
   </si>
   <si>
@@ -599,9 +590,6 @@
     <t>P23B</t>
   </si>
   <si>
-    <t>P23A</t>
-  </si>
-  <si>
     <t>mauvaises coordonnées pour 2024, égales à celle de P2</t>
   </si>
   <si>
@@ -1268,9 +1256,6 @@
     <t>info_points_2026</t>
   </si>
   <si>
-    <t>Informations relatives aux enclos ayant été posés en 202026 ainsi qu'aux placettes ayant fait l'objet de relevé phytosociologique</t>
-  </si>
-  <si>
     <t>Id enclos-exclos selon la nouvelle nomenclature : P (prairie) + ancien numéro + lettre correspondant à un déplacement effectué entre deux années</t>
   </si>
   <si>
@@ -1307,15 +1292,6 @@
     <t>PRELEV_CERF_ELAPHE_100HA</t>
   </si>
   <si>
-    <t>Nombre de chevreuils prélevés sur la commune pour 100 ha</t>
-  </si>
-  <si>
-    <t>Nombre de cerfs élaphe femelles prélevés sur la commune pour 100 ha</t>
-  </si>
-  <si>
-    <t>Nombre de cerfs élaphe (mâles et femelles confondus) prélevés sur la commune pour 100 ha</t>
-  </si>
-  <si>
     <t>ALTI</t>
   </si>
   <si>
@@ -1325,15 +1301,6 @@
     <t>SURF_BAT_250</t>
   </si>
   <si>
-    <t>Identifiant de la placette forestière la plus proche (avec présence de sous-étage)</t>
-  </si>
-  <si>
-    <t>Distance à la placette forestière la plus proche (avec présence de sous-étage)</t>
-  </si>
-  <si>
-    <t>Abroutissement moyen de la placette forestière la plus proche (avec présence de sous-étage)</t>
-  </si>
-  <si>
     <t>Proportion de forêt dans une zone tampon de 250m (source : BD Forêt v2 – IGN)</t>
   </si>
   <si>
@@ -1365,13 +1332,157 @@
   </si>
   <si>
     <t>Surface (m²) couverte par des bâtiments dans une zone tampon de 500m (source : BD TOPO – IGN)</t>
+  </si>
+  <si>
+    <t>Informations relatives aux enclos ayant été posés en 2026 ainsi qu'aux placettes ayant fait l'objet de relevé phytosociologique</t>
+  </si>
+  <si>
+    <t>Coordonnée métrique X approximative (Lambert 93)</t>
+  </si>
+  <si>
+    <t>Coordonnée métrique Y approximative (Lambert 93)</t>
+  </si>
+  <si>
+    <t>Commune</t>
+  </si>
+  <si>
+    <t>Lieu-dit ou hameau, peu être identique à nom_parcellle</t>
+  </si>
+  <si>
+    <t>Précision toponymique du lieu_dit</t>
+  </si>
+  <si>
+    <t>pose_202X</t>
+  </si>
+  <si>
+    <t>Pose effective de l'enclos durant l'année 202X (NB : les enclos peuvent avoir été déplacés)</t>
+  </si>
+  <si>
+    <t>Nombre de chevreuils prélevés sur la commune pour 100 ha (saison de chasse 2024-2025)</t>
+  </si>
+  <si>
+    <t>Nombre de cerfs élaphe femelles prélevés sur la commune pour 100 ha (saison de chasse 2024-2025)</t>
+  </si>
+  <si>
+    <t>Nombre de cerfs élaphe (mâles et femelles confondus) prélevés sur la commune pour 100 ha (saison de chasse 2024-2025)</t>
+  </si>
+  <si>
+    <t>Températures moyennes (°C) calculées par modélisation (Briswalter 2021, Piedallu 2023) pour l’hiver 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Températures moyennes (°C) calculées par modélisation (Briswalter 2021, Piedallu 2023) pour le printemps 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Températures minimales (°C) calculées par modélisation (Briswalter 2021, Piedallu 2023) pour l’hiver 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Températures minimales (°C) calculées par modélisation (Briswalter 2021, Piedallu 2023) pour le printemps 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Températures maximales (°C) calculées par modélisation (Briswalter 2021, Piedallu 2023) pour l’hiver 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Températures maximales (°C) calculées par modélisation (Briswalter 2021, Piedallu 2023) pour le printemps 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Réserve utile des sol calculée par modélisation (Briswalter 2021, Piedallu 2023) pour l’hiver 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Réserve utile des sol calculée par modélisation (Briswalter 2021, Piedallu 2023) pour le printemps 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Évapotranspiration potentielle calculée avec la formule de Turc (mm) (Piedallu et al, 2013) pour l’hiver 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Évapotranspiration potentielle calculée avec la formule de Turc (mm) (Piedallu et al, 2013) pour le printemps 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Bilan hydrique climatique (P-ETP, mm) extrapolé pour l’hiver 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Bilan hydrique climatique (P-ETP, mm) extrapolé pour le printemps 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Précipitations (mm) extrapolées par krigeage pour l’hiver 2024 (source : Digitalis – UMR SILVA) (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Précipitations (mm) extrapolées par krigeage pour le printemps 2024 (source : Digitalis – UMR SILVA) (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Déficit d'évaporation en eau des sols calculé avec la formule de Thornthwaite (etp-etr, mm) (Piedallu et al,  2013, 2019) pour l’hiver 2024 (source : Digitalis – UMR SILVA)</t>
+  </si>
+  <si>
+    <t>Exposition (°) calculée à partir du MNT</t>
+  </si>
+  <si>
+    <t>Altitude (m) calculée à partir du MNT</t>
+  </si>
+  <si>
+    <t>Identifiant de la placette forestière 2026 la plus proche</t>
+  </si>
+  <si>
+    <t>Abroutissement moyen (%) de la placette forestirèe 2026 la plus proche</t>
+  </si>
+  <si>
+    <t>Distance à la placette forestière la plus proche</t>
+  </si>
+  <si>
+    <t>tableau_floristique</t>
+  </si>
+  <si>
+    <t>&lt;5%, peu d'individus</t>
+  </si>
+  <si>
+    <t>&lt;5%, nombreux individus</t>
+  </si>
+  <si>
+    <t>5 à 25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 à 50% </t>
+  </si>
+  <si>
+    <t>50 à 75%</t>
+  </si>
+  <si>
+    <t>75 à 100%</t>
+  </si>
+  <si>
+    <t>Tableau d'abondance-dominance issu du relevé phytosociologique (classes de recouvrement ci-dessous)</t>
+  </si>
+  <si>
+    <t>biomasses</t>
+  </si>
+  <si>
+    <t>Données des prélévements de biomasse depuis 2020</t>
+  </si>
+  <si>
+    <t>Date de pose de l'enclos (la donnée peut être manquante)</t>
+  </si>
+  <si>
+    <t>Année du prélévement</t>
+  </si>
+  <si>
+    <t>Date du prélévement</t>
+  </si>
+  <si>
+    <t>Nombre de jours entre la pose de l'enclos et le prélévement</t>
+  </si>
+  <si>
+    <t>Pourcentage de pertes entre l'enclos et l'exclos (pertes = (mf_tot_enclos - mf_tot_exclos) / mf_tot_enclos)</t>
+  </si>
+  <si>
+    <t>Masse fraiche des 6 quadrarts à l'intérieur de l'enclos (g)</t>
+  </si>
+  <si>
+    <t>Masse fraiche des 6 quadrarts de l'exclos (g)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1432,9 +1543,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="4" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1457,7 +1576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1496,7 +1615,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1777,19 +1904,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D906645A-0B29-4559-A5E0-8CAB7DCA4876}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" style="13" customWidth="1"/>
+    <col min="1" max="1" width="36.140625" style="13" customWidth="1"/>
     <col min="2" max="2" width="132.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1797,199 +1924,540 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>417</v>
+      <c r="A11" s="14" t="s">
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>418</v>
+      <c r="A12" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>419</v>
+      <c r="A13" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>349</v>
+      <c r="A14" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>350</v>
+      <c r="A15" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>351</v>
+      <c r="A16" s="14" t="s">
+        <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>352</v>
+      <c r="A17" s="14" t="s">
+        <v>301</v>
       </c>
       <c r="B17" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>353</v>
+      <c r="A18" s="14" t="s">
+        <v>435</v>
       </c>
       <c r="B18" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>354</v>
+      <c r="A19" s="14" t="s">
+        <v>202</v>
       </c>
       <c r="B19" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="B20" t="s">
-        <v>435</v>
+      <c r="A20" s="14" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>356</v>
+      <c r="A21" s="12" t="s">
+        <v>412</v>
       </c>
       <c r="B21" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>357</v>
+      <c r="A22" s="12" t="s">
+        <v>413</v>
       </c>
       <c r="B22" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>425</v>
+      <c r="A23" s="12" t="s">
+        <v>414</v>
       </c>
       <c r="B23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>358</v>
+      <c r="A24" s="14" t="s">
+        <v>302</v>
       </c>
       <c r="B24" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>359</v>
+        <v>307</v>
       </c>
       <c r="B25" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="B26" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="B27" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B28" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="B29" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="B30" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="B31" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="B32" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="B33" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B34" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="B35" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="B36" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="B37" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="B38" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="B39" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="B40" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="B41" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="B42" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>347</v>
+      </c>
+      <c r="B43" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="B44" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="B45" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="B46" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="B47" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="B48" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="B49" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="B50" t="s">
         <v>427</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B51" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="B52" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="B53" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
+        <v>357</v>
+      </c>
+      <c r="B54" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="16">
+        <v>1</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="16">
+        <v>2</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="16">
+        <v>3</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="16">
+        <v>4</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="16">
+        <v>5</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B70" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B71" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B72" t="s">
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -2018,33 +2486,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -2056,13 +2524,13 @@
         <v>6383406.9179999996</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>2</v>
@@ -2070,7 +2538,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B3" s="3">
         <v>2</v>
@@ -2082,13 +2550,13 @@
         <v>6379835.8499999996</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>2</v>
@@ -2096,7 +2564,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
@@ -2108,13 +2576,13 @@
         <v>6382897.1100000003</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>4</v>
@@ -2122,7 +2590,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -2134,21 +2602,21 @@
         <v>6379980.4369999999</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" s="3">
         <v>5</v>
@@ -2160,13 +2628,13 @@
         <v>6379296.1900000004</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>6</v>
@@ -2174,7 +2642,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B7" s="3">
         <v>7</v>
@@ -2186,13 +2654,13 @@
         <v>6379599.0999999996</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>10</v>
@@ -2200,7 +2668,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B8" s="3">
         <v>8</v>
@@ -2212,13 +2680,13 @@
         <v>6380657.8969999999</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>12</v>
@@ -2226,7 +2694,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -2238,13 +2706,13 @@
         <v>6381467.2800000003</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>12</v>
@@ -2252,7 +2720,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" s="3">
         <v>10</v>
@@ -2264,13 +2732,13 @@
         <v>6381221.0099999998</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>13</v>
@@ -2278,19 +2746,19 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>15</v>
@@ -2298,7 +2766,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B12" s="3">
         <v>12</v>
@@ -2310,13 +2778,13 @@
         <v>6382400.0690000001</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>17</v>
@@ -2324,7 +2792,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B13" s="3">
         <v>13</v>
@@ -2336,13 +2804,13 @@
         <v>6382754.3399999999</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>17</v>
@@ -2350,7 +2818,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B14" s="3">
         <v>15</v>
@@ -2362,13 +2830,13 @@
         <v>6383896.2479999997</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>20</v>
@@ -2376,7 +2844,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B15" s="3">
         <v>18</v>
@@ -2388,13 +2856,13 @@
         <v>6384928.7599999998</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>25</v>
@@ -2402,7 +2870,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B16" s="3">
         <v>19</v>
@@ -2414,21 +2882,21 @@
         <v>6389367.4170000004</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B17" s="3">
         <v>20</v>
@@ -2440,21 +2908,21 @@
         <v>6388340.3600000003</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B18" s="3">
         <v>21</v>
@@ -2466,13 +2934,13 @@
         <v>6388994.6140000001</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>6</v>
@@ -2480,7 +2948,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B19" s="3">
         <v>22</v>
@@ -2492,13 +2960,13 @@
         <v>6388277.6500000004</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>6</v>
@@ -2506,7 +2974,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B20" s="3">
         <v>23</v>
@@ -2518,21 +2986,21 @@
         <v>6384900.0199999996</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C21" s="3">
         <v>693846.48</v>
@@ -2541,24 +3009,24 @@
         <v>6385161.9400000004</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="G21" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C22" s="3">
         <v>694107.65099999995</v>
@@ -2567,21 +3035,21 @@
         <v>6384839.0659999996</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B23" s="3">
         <v>25</v>
@@ -2593,13 +3061,13 @@
         <v>6384508.5760000004</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>36</v>
@@ -2607,7 +3075,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B24" s="3">
         <v>26</v>
@@ -2619,13 +3087,13 @@
         <v>6385272.79</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="G24" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>39</v>
@@ -2633,7 +3101,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B25" s="3">
         <v>27</v>
@@ -2645,13 +3113,13 @@
         <v>6384887.0619999999</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="G25" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>41</v>
@@ -2659,7 +3127,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B26" s="3">
         <v>28</v>
@@ -2671,13 +3139,13 @@
         <v>6385803.04</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>44</v>
@@ -2685,7 +3153,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B27" s="3">
         <v>29</v>
@@ -2697,13 +3165,13 @@
         <v>6385140.2620000001</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>44</v>
@@ -2711,7 +3179,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B28" s="3">
         <v>30</v>
@@ -2723,13 +3191,13 @@
         <v>6389667.25</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>47</v>
@@ -2737,7 +3205,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C29" s="3">
         <v>694072.18</v>
@@ -2746,13 +3214,13 @@
         <v>6390128.0199999996</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>51</v>
@@ -2760,7 +3228,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B30" s="3">
         <v>33</v>
@@ -2772,13 +3240,13 @@
         <v>6385232.1909999996</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>52</v>
@@ -2786,7 +3254,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B31" s="3">
         <v>34</v>
@@ -2798,13 +3266,13 @@
         <v>6383747.0300000003</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>54</v>
@@ -2812,25 +3280,25 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B32" s="3">
         <v>35</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>54</v>
@@ -2838,7 +3306,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B33" s="3">
         <v>36</v>
@@ -2850,13 +3318,13 @@
         <v>6385804.3600000003</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>54</v>
@@ -2864,7 +3332,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B34" s="3">
         <v>10</v>
@@ -2876,19 +3344,19 @@
         <v>6381221.0099999998</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2926,240 +3394,240 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="G1" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q1" s="10" t="s">
+      <c r="X1" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="AT1" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="BC1" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="BD1" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="BE1" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="BF1" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="BG1" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="BH1" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="BI1" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="BJ1" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="BK1" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="BL1" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="BM1" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="BN1" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="BO1" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="BP1" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="BQ1" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="BR1" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="BS1" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="BT1" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="BU1" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="BV1" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="R1" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="S1" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="AO1" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="AP1" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AQ1" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="AR1" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="AS1" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="AT1" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="AU1" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="AV1" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="AW1" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="AX1" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="AY1" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="AZ1" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="BA1" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="BB1" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="BC1" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="BD1" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="BE1" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="BF1" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="BG1" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="BH1" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="BI1" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="BJ1" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="BK1" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="BL1" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="BM1" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="BN1" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="BO1" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="BP1" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="BQ1" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BW1" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BX1" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BY1" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="BV1" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="BW1" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="BX1" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="BY1" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="BZ1" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B2" s="4">
         <v>689936.65</v>
@@ -3171,7 +3639,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>14</v>
@@ -3180,28 +3648,28 @@
         <v>14</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="M2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q2">
         <v>0.52851000000000004</v>
@@ -3378,7 +3846,7 @@
         <v>2804.4744599999999</v>
       </c>
       <c r="BX2" s="3" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="BY2" s="3">
         <v>8.4058641975308603</v>
@@ -3389,7 +3857,7 @@
     </row>
     <row r="3" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B3" s="4">
         <v>688697</v>
@@ -3401,37 +3869,37 @@
         <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q3">
         <v>0.52851000000000004</v>
@@ -3611,7 +4079,7 @@
         <v>394.90603800000002</v>
       </c>
       <c r="BX3" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="BY3" s="3">
         <v>21.625330096260299</v>
@@ -3622,7 +4090,7 @@
     </row>
     <row r="4" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="4">
         <v>688963.4</v>
@@ -3634,31 +4102,31 @@
         <v>15</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q4">
         <v>0.52851000000000004</v>
@@ -3835,7 +4303,7 @@
         <v>4711.64887</v>
       </c>
       <c r="BX4" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="BY4" s="3">
         <v>21.625330096260299</v>
@@ -3846,7 +4314,7 @@
     </row>
     <row r="5" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="4">
         <v>692199.87</v>
@@ -3858,7 +4326,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>18</v>
@@ -3867,28 +4335,28 @@
         <v>18</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="L5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="Q5">
         <v>0.52851000000000004</v>
@@ -4068,7 +4536,7 @@
         <v>3052.7512900000002</v>
       </c>
       <c r="BX5" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="BY5" s="3">
         <v>64.6666666666667</v>
@@ -4079,7 +4547,7 @@
     </row>
     <row r="6" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B6" s="4">
         <v>688488.03</v>
@@ -4091,34 +4559,34 @@
         <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q6">
         <v>0.52851000000000004</v>
@@ -4298,7 +4766,7 @@
         <v>90.160760600000003</v>
       </c>
       <c r="BX6" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="BY6" s="3">
         <v>1.3333333333333299</v>
@@ -4309,7 +4777,7 @@
     </row>
     <row r="7" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B7" s="4">
         <v>690807.68</v>
@@ -4318,40 +4786,40 @@
         <v>6383435.6600000001</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Q7">
         <v>0.52851000000000004</v>
@@ -4525,7 +4993,7 @@
         <v>500.48089700000003</v>
       </c>
       <c r="BX7" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="BY7" s="3">
         <v>60.514907901046499</v>
@@ -4536,7 +5004,7 @@
     </row>
     <row r="8" spans="1:78" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B8" s="4">
         <v>696256.55</v>
@@ -4554,31 +5022,31 @@
         <v>22</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="Q8">
         <v>0.64295000000000002</v>
@@ -4752,7 +5220,7 @@
         <v>792.23223299999995</v>
       </c>
       <c r="BX8" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="BY8" s="3">
         <v>69.316088840736697</v>
@@ -4763,7 +5231,7 @@
     </row>
     <row r="9" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B9" s="4">
         <v>695909.02</v>
@@ -4782,31 +5250,31 @@
         <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="Q9">
         <v>0.64295000000000002</v>
@@ -4986,7 +5454,7 @@
         <v>67.749554000000003</v>
       </c>
       <c r="BX9" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="BY9" s="3">
         <v>69.316088840736697</v>
@@ -4997,7 +5465,7 @@
     </row>
     <row r="10" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B10" s="4">
         <v>692722.23</v>
@@ -5015,28 +5483,28 @@
         <v>26</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="M10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q10">
         <v>0.12987000000000001</v>
@@ -5216,7 +5684,7 @@
         <v>580.12323800000001</v>
       </c>
       <c r="BX10" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="BY10" s="3">
         <v>61.25</v>
@@ -5227,7 +5695,7 @@
     </row>
     <row r="11" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B11" s="4">
         <v>692741.86399999994</v>
@@ -5245,28 +5713,28 @@
         <v>29</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q11">
         <v>0.12987000000000001</v>
@@ -5443,7 +5911,7 @@
         <v>59.063750300000002</v>
       </c>
       <c r="BX11" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="BY11" s="3">
         <v>13.7274305555556</v>
@@ -5454,7 +5922,7 @@
     </row>
     <row r="12" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B12" s="4">
         <v>691887</v>
@@ -5466,37 +5934,37 @@
         <v>2</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="Q12">
         <v>0.52851000000000004</v>
@@ -5676,7 +6144,7 @@
         <v>1298.6376600000001</v>
       </c>
       <c r="BX12" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="BY12" s="3">
         <v>64.6666666666667</v>
@@ -5687,7 +6155,7 @@
     </row>
     <row r="13" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B13" s="4">
         <v>692031.87</v>
@@ -5699,34 +6167,34 @@
         <v>2</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N13" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q13">
         <v>0.52851000000000004</v>
@@ -5906,7 +6374,7 @@
         <v>1298.6376600000001</v>
       </c>
       <c r="BX13" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="BY13" s="3">
         <v>44.6666666666667</v>
@@ -5917,7 +6385,7 @@
     </row>
     <row r="14" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B14" s="4">
         <v>692211.78</v>
@@ -5929,34 +6397,34 @@
         <v>2</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="O14" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q14">
         <v>0.52851000000000004</v>
@@ -6133,7 +6601,7 @@
         <v>785.48353899999995</v>
       </c>
       <c r="BX14" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="BY14" s="3">
         <v>44.6666666666667</v>
@@ -6144,7 +6612,7 @@
     </row>
     <row r="15" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B15" s="4">
         <v>691809.39</v>
@@ -6153,37 +6621,37 @@
         <v>6379835.8499999996</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="M15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M15" s="6" t="s">
+      <c r="O15" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="Q15">
         <v>0.52851000000000004</v>
@@ -6357,7 +6825,7 @@
         <v>506.44396999999998</v>
       </c>
       <c r="BX15" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BY15" s="3">
         <v>0.94727272727272704</v>
@@ -6368,7 +6836,7 @@
     </row>
     <row r="16" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B16" s="4">
         <v>693449.65</v>
@@ -6377,7 +6845,7 @@
         <v>6388339.8099999996</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -6389,28 +6857,28 @@
         <v>29</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q16">
         <v>0.12987000000000001</v>
@@ -6590,7 +7058,7 @@
         <v>9213.68462</v>
       </c>
       <c r="BX16" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="BY16" s="3">
         <v>31.6071428571429</v>
@@ -6601,7 +7069,7 @@
     </row>
     <row r="17" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B17" s="4">
         <v>696269.64</v>
@@ -6622,31 +7090,31 @@
         <v>31</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Q17">
         <v>0.12987000000000001</v>
@@ -6826,7 +7294,7 @@
         <v>646.19124899999997</v>
       </c>
       <c r="BX17" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="BY17" s="3">
         <v>6.765625</v>
@@ -6837,7 +7305,7 @@
     </row>
     <row r="18" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B18" s="4">
         <v>697826.36399999994</v>
@@ -6858,31 +7326,31 @@
         <v>33</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="Q18">
         <v>0.12987000000000001</v>
@@ -7062,7 +7530,7 @@
         <v>2957.8354300000001</v>
       </c>
       <c r="BX18" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="BY18" s="3">
         <v>7.67166095890411</v>
@@ -7073,7 +7541,7 @@
     </row>
     <row r="19" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B19" s="4">
         <v>694815.31</v>
@@ -7082,7 +7550,7 @@
         <v>6384900.0199999996</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -7094,31 +7562,31 @@
         <v>34</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>0.12987000000000001</v>
@@ -7295,7 +7763,7 @@
         <v>1160.94451</v>
       </c>
       <c r="BX19" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="BY19" s="3">
         <v>81.176019996774698</v>
@@ -7306,7 +7774,7 @@
     </row>
     <row r="20" spans="1:78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B20" s="4">
         <v>693846.48</v>
@@ -7321,37 +7789,37 @@
         <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>37</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O20" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="O20" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="P20" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Q20">
         <v>0.12987000000000001</v>
@@ -7528,7 +7996,7 @@
         <v>588.52813800000001</v>
       </c>
       <c r="BX20" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="BY20" s="3">
         <v>81.176019996774698</v>
@@ -7539,7 +8007,7 @@
     </row>
     <row r="21" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B21" s="4">
         <v>694107.65099999995</v>
@@ -7554,34 +8022,34 @@
         <v>27</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="O21" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="Q21">
         <v>0.12987000000000001</v>
@@ -7758,7 +8226,7 @@
         <v>2078.0604199999998</v>
       </c>
       <c r="BX21" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="BY21" s="3">
         <v>81.176019996774698</v>
@@ -7769,7 +8237,7 @@
     </row>
     <row r="22" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B22" s="4">
         <v>694338.81599999999</v>
@@ -7784,34 +8252,34 @@
         <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>38</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M22" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="M22" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="N22" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q22">
         <v>0.12987000000000001</v>
@@ -7988,7 +8456,7 @@
         <v>1629.9331199999999</v>
       </c>
       <c r="BX22" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="BY22" s="3">
         <v>81.176019996774698</v>
@@ -7999,7 +8467,7 @@
     </row>
     <row r="23" spans="1:78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B23" s="4">
         <v>693208.77</v>
@@ -8017,31 +8485,31 @@
         <v>40</v>
       </c>
       <c r="G23" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M23" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O23" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="Q23">
         <v>0.12987000000000001</v>
@@ -8221,7 +8689,7 @@
         <v>2578.5543899999998</v>
       </c>
       <c r="BX23" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="BY23" s="3">
         <v>3.14509246088193</v>
@@ -8232,7 +8700,7 @@
     </row>
     <row r="24" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B24" s="4">
         <v>695955.37</v>
@@ -8253,28 +8721,28 @@
         <v>43</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O24" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="P24" s="5"/>
       <c r="Q24">
@@ -8449,7 +8917,7 @@
         <v>766.76734699999997</v>
       </c>
       <c r="BX24" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="BY24" s="3">
         <v>25.5</v>
@@ -8460,7 +8928,7 @@
     </row>
     <row r="25" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B25" s="4">
         <v>694865.09</v>
@@ -8481,31 +8949,31 @@
         <v>45</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="K25" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="Q25">
         <v>0.12987000000000001</v>
@@ -8679,7 +9147,7 @@
         <v>1069.45605</v>
       </c>
       <c r="BX25" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="BY25" s="3">
         <v>20.518783573650001</v>
@@ -8690,7 +9158,7 @@
     </row>
     <row r="26" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B26" s="4">
         <v>696678.66500000004</v>
@@ -8711,31 +9179,31 @@
         <v>46</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="L26" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="M26" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N26" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Q26">
         <v>0.12987000000000001</v>
@@ -8912,7 +9380,7 @@
         <v>39.589601700000003</v>
       </c>
       <c r="BX26" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="BY26" s="3">
         <v>25.5</v>
@@ -8923,7 +9391,7 @@
     </row>
     <row r="27" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B27" s="4">
         <v>692457</v>
@@ -8938,34 +9406,34 @@
         <v>27</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="Q27">
         <v>0.12987000000000001</v>
@@ -9145,7 +9613,7 @@
         <v>4164.0756199999996</v>
       </c>
       <c r="BX27" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="BY27" s="3">
         <v>31.6071428571429</v>
@@ -9156,7 +9624,7 @@
     </row>
     <row r="28" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B28" s="4">
         <v>696425.05</v>
@@ -9171,37 +9639,37 @@
         <v>27</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="M28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O28" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="Q28">
         <v>0.12987000000000001</v>
@@ -9381,7 +9849,7 @@
         <v>850.38795100000004</v>
       </c>
       <c r="BX28" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="BY28" s="3">
         <v>87.5</v>
@@ -9392,7 +9860,7 @@
     </row>
     <row r="29" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B29" s="4">
         <v>694420.11</v>
@@ -9413,28 +9881,28 @@
         <v>50</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N29" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q29">
         <v>0.12987000000000001</v>
@@ -9614,7 +10082,7 @@
         <v>6442.47433</v>
       </c>
       <c r="BX29" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="BY29" s="3">
         <v>81.176019996774698</v>
@@ -9625,7 +10093,7 @@
     </row>
     <row r="30" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B30" s="4">
         <v>693857</v>
@@ -9640,31 +10108,31 @@
         <v>27</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30">
@@ -9845,7 +10313,7 @@
         <v>1420.34961</v>
       </c>
       <c r="BX30" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BY30" s="3">
         <v>22.875</v>
@@ -9856,7 +10324,7 @@
     </row>
     <row r="31" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B31" s="4">
         <v>694072.18</v>
@@ -9871,31 +10339,31 @@
         <v>27</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="L31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O31" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O31" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="Q31">
         <v>0.12987000000000001</v>
@@ -10069,7 +10537,7 @@
         <v>161.945526</v>
       </c>
       <c r="BX31" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="BY31" s="3">
         <v>22.875</v>
@@ -10080,7 +10548,7 @@
     </row>
     <row r="32" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B32" s="4">
         <v>694729.68400000001</v>
@@ -10095,34 +10563,34 @@
         <v>27</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O32" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q32">
         <v>0.12987000000000001</v>
@@ -10302,7 +10770,7 @@
         <v>8948.2956099999992</v>
       </c>
       <c r="BX32" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="BY32" s="3">
         <v>81.176019996774698</v>
@@ -10313,7 +10781,7 @@
     </row>
     <row r="33" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B33" s="4">
         <v>693362.96</v>
@@ -10331,31 +10799,31 @@
         <v>55</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="K33" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q33">
         <v>0.12987000000000001</v>
@@ -10535,7 +11003,7 @@
         <v>6833.8493099999996</v>
       </c>
       <c r="BX33" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="BY33" s="3">
         <v>12.038461538461499</v>
@@ -10546,7 +11014,7 @@
     </row>
     <row r="34" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B34" s="4">
         <v>693927.25</v>
@@ -10567,28 +11035,28 @@
         <v>57</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O34" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q34">
         <v>0.12987000000000001</v>
@@ -10765,7 +11233,7 @@
         <v>703.07739500000002</v>
       </c>
       <c r="BX34" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BY34" s="3">
         <v>56.988407224958898</v>
@@ -10776,7 +11244,7 @@
     </row>
     <row r="35" spans="1:78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B35" s="4">
         <v>694022</v>
@@ -10797,28 +11265,28 @@
         <v>57</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="K35" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="L35" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q35">
         <v>0.12987000000000001</v>
@@ -10995,7 +11463,7 @@
         <v>7.4334119300000001</v>
       </c>
       <c r="BX35" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="BY35" s="3">
         <v>56.988407224958898</v>
@@ -11006,7 +11474,7 @@
     </row>
     <row r="36" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B36" s="4">
         <v>698217.18</v>
@@ -11027,28 +11495,28 @@
         <v>58</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="L36" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="M36" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K36" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N36" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O36" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q36">
         <v>0.12987000000000001</v>
@@ -11228,7 +11696,7 @@
         <v>2045.98975</v>
       </c>
       <c r="BX36" s="3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="BY36" s="3">
         <v>87.5</v>
@@ -11239,7 +11707,7 @@
     </row>
     <row r="37" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B37" s="4">
         <v>692056</v>
@@ -11260,28 +11728,28 @@
         <v>61</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O37" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O37" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="Q37">
         <v>0.12987000000000001</v>
@@ -11458,7 +11926,7 @@
         <v>2476.0663599999998</v>
       </c>
       <c r="BX37" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="BY37" s="3">
         <v>61.25</v>
@@ -11469,7 +11937,7 @@
     </row>
     <row r="38" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B38" s="4">
         <v>694459.45</v>
@@ -11487,28 +11955,28 @@
         <v>50</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O38" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q38">
         <v>0.12987000000000001</v>
@@ -11688,7 +12156,7 @@
         <v>7794.6334699999998</v>
       </c>
       <c r="BX38" s="3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="BY38" s="3">
         <v>81.176019996774698</v>
@@ -11699,7 +12167,7 @@
     </row>
     <row r="39" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B39" s="4">
         <v>697391.72</v>
@@ -11708,7 +12176,7 @@
         <v>6390262.3799999999</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>27</v>
@@ -11717,28 +12185,28 @@
         <v>63</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q39">
         <v>0.12987000000000001</v>
@@ -11918,7 +12386,7 @@
         <v>808.11576700000001</v>
       </c>
       <c r="BX39" s="3" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="BY39" s="3">
         <v>73.375</v>
@@ -11929,7 +12397,7 @@
     </row>
     <row r="40" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B40" s="4">
         <v>690981.48</v>
@@ -11941,34 +12409,34 @@
         <v>4</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O40" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q40">
         <v>0.52851000000000004</v>
@@ -12148,7 +12616,7 @@
         <v>1680.0237199999999</v>
       </c>
       <c r="BX40" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="BY40" s="3">
         <v>70.134909031838902</v>
@@ -12159,7 +12627,7 @@
     </row>
     <row r="41" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B41" s="4">
         <v>690899.52</v>
@@ -12171,34 +12639,34 @@
         <v>4</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="L41" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J41" s="5" t="s">
+      <c r="M41" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N41" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q41">
         <v>0.52851000000000004</v>
@@ -12378,7 +12846,7 @@
         <v>864.761439</v>
       </c>
       <c r="BX41" s="3" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="BY41" s="3">
         <v>70.134909031838902</v>
@@ -12389,7 +12857,7 @@
     </row>
     <row r="42" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B42" s="4">
         <v>689642.701</v>
@@ -12398,37 +12866,37 @@
         <v>6379980.4369999999</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O42" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q42">
         <v>0.52851000000000004</v>
@@ -12608,7 +13076,7 @@
         <v>4137.9733800000004</v>
       </c>
       <c r="BX42" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="BY42" s="3">
         <v>9.1359649122807003</v>
@@ -12619,7 +13087,7 @@
     </row>
     <row r="43" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B43" s="4">
         <v>696138</v>
@@ -12634,31 +13102,31 @@
         <v>21</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K43" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O43" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O43" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="Q43">
         <v>0.64295000000000002</v>
@@ -12838,7 +13306,7 @@
         <v>67.749554000000003</v>
       </c>
       <c r="BX43" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="BY43" s="3">
         <v>69.316088840736697</v>
@@ -12849,7 +13317,7 @@
     </row>
     <row r="44" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B44" s="4">
         <v>691739.3</v>
@@ -12861,7 +13329,7 @@
         <v>6</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>7</v>
@@ -12870,28 +13338,28 @@
         <v>7</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="L44" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="M44" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N44" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O44" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q44">
         <v>0.52851000000000004</v>
@@ -13071,7 +13539,7 @@
         <v>5141.59728</v>
       </c>
       <c r="BX44" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="BY44" s="3">
         <v>0.94727272727272704</v>
@@ -13082,7 +13550,7 @@
     </row>
     <row r="45" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B45" s="4">
         <v>689916.83</v>
@@ -13094,37 +13562,37 @@
         <v>8</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q45">
         <v>0.52851000000000004</v>
@@ -13304,7 +13772,7 @@
         <v>6211.3302800000001</v>
       </c>
       <c r="BX45" s="3" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="BY45" s="3">
         <v>70.8333333333333</v>
@@ -13315,7 +13783,7 @@
     </row>
     <row r="46" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B46" s="4">
         <v>688952.44</v>
@@ -13327,37 +13795,37 @@
         <v>10</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O46" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q46">
         <v>0.52851000000000004</v>
@@ -13537,7 +14005,7 @@
         <v>6727.1791499999999</v>
       </c>
       <c r="BX46" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="BY46" s="3">
         <v>21.625330096260299</v>
@@ -13548,7 +14016,7 @@
     </row>
     <row r="47" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B47" s="4">
         <v>689451.36</v>
@@ -13560,34 +14028,34 @@
         <v>10</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H47" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N47" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q47">
         <v>0.52851000000000004</v>
@@ -13764,7 +14232,7 @@
         <v>5596.3815100000002</v>
       </c>
       <c r="BX47" s="3" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="BY47" s="3">
         <v>1.4274611398963699</v>
@@ -13775,7 +14243,7 @@
     </row>
     <row r="48" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B48" s="4">
         <v>688875.08</v>
@@ -13784,37 +14252,37 @@
         <v>6380454.0700000003</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q48">
         <v>0.52851000000000004</v>
@@ -13991,7 +14459,7 @@
         <v>2785.7712700000002</v>
       </c>
       <c r="BX48" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="BY48" s="3">
         <v>21.625330096260299</v>
@@ -14002,7 +14470,7 @@
     </row>
     <row r="49" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B49" s="4">
         <v>689080.99</v>
@@ -14011,37 +14479,37 @@
         <v>6380568.1600000001</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H49" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="K49" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="L49" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q49">
         <v>0.52851000000000004</v>
@@ -14221,7 +14689,7 @@
         <v>6084.1993400000001</v>
       </c>
       <c r="BX49" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="BY49" s="3">
         <v>21.625330096260299</v>
@@ -14232,7 +14700,7 @@
     </row>
     <row r="50" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B50" s="4">
         <v>688885.01100000006</v>
@@ -14241,40 +14709,40 @@
         <v>6380657.8969999999</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H50" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M50" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="N50" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="O50" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="K50" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="O50" s="7" t="s">
-        <v>82</v>
-      </c>
       <c r="P50" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Q50">
         <v>0.52851000000000004</v>
@@ -14454,7 +14922,7 @@
         <v>3402.9304900000002</v>
       </c>
       <c r="BX50" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="BY50" s="3">
         <v>21.625330096260299</v>
@@ -14465,7 +14933,7 @@
     </row>
     <row r="51" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B51" s="4">
         <v>691354.4</v>
@@ -14474,37 +14942,37 @@
         <v>6381467.2800000003</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K51" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="L51" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="M51" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K51" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N51" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q51">
         <v>0.52851000000000004</v>
@@ -14684,7 +15152,7 @@
         <v>3064.6159699999998</v>
       </c>
       <c r="BX51" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="BY51" s="3">
         <v>11.3470160791589</v>
@@ -14695,7 +15163,7 @@
     </row>
     <row r="52" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B52" s="4">
         <v>698217.18</v>
@@ -14716,34 +15184,219 @@
         <v>58</v>
       </c>
       <c r="H52" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="M52" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="N52" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="O52" s="7" t="str">
-        <f>IF(ISNUMBER(MATCH(A52, tableau_floristique!B$1:AJ$1, 0)), "OUI","NON")</f>
-        <v>OUI</v>
+        <v>81</v>
+      </c>
+      <c r="O52" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q52">
+        <v>0.12987000000000001</v>
+      </c>
+      <c r="R52" s="3">
+        <v>1</v>
+      </c>
+      <c r="S52" s="3">
+        <v>3.3376600000000001</v>
+      </c>
+      <c r="T52" s="3">
+        <v>36</v>
+      </c>
+      <c r="U52" s="3">
+        <v>81</v>
+      </c>
+      <c r="V52" s="3">
+        <v>87</v>
+      </c>
+      <c r="W52" s="3">
+        <v>65</v>
+      </c>
+      <c r="X52" s="3">
+        <v>92</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>78</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>-8</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>28</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>32</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>10</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>34</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>30</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>77</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>131</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>139</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>117</v>
+      </c>
+      <c r="AJ52" s="3">
+        <v>146</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>123</v>
+      </c>
+      <c r="AL52" s="3">
+        <v>609</v>
+      </c>
+      <c r="AM52" s="3">
+        <v>609</v>
+      </c>
+      <c r="AN52" s="3">
+        <v>388</v>
+      </c>
+      <c r="AO52" s="3">
+        <v>482</v>
+      </c>
+      <c r="AP52" s="3">
+        <v>501</v>
+      </c>
+      <c r="AQ52" s="3">
+        <v>609</v>
+      </c>
+      <c r="AR52" s="3">
+        <v>187</v>
+      </c>
+      <c r="AS52" s="3">
+        <v>756</v>
+      </c>
+      <c r="AT52" s="3">
+        <v>788</v>
+      </c>
+      <c r="AU52" s="3">
+        <v>654</v>
+      </c>
+      <c r="AV52" s="3">
+        <v>825</v>
+      </c>
+      <c r="AW52" s="3">
+        <v>691</v>
+      </c>
+      <c r="AX52" s="3">
+        <v>693</v>
+      </c>
+      <c r="AY52" s="3">
+        <v>345</v>
+      </c>
+      <c r="AZ52" s="3">
+        <v>-419</v>
+      </c>
+      <c r="BA52" s="3">
+        <v>-41</v>
+      </c>
+      <c r="BB52" s="3">
+        <v>-62</v>
+      </c>
+      <c r="BC52" s="3">
+        <v>466</v>
+      </c>
+      <c r="BD52" s="3">
+        <v>3338</v>
+      </c>
+      <c r="BE52" s="3">
+        <v>1111</v>
+      </c>
+      <c r="BF52" s="3">
+        <v>1840</v>
+      </c>
+      <c r="BG52" s="3">
+        <v>2293</v>
+      </c>
+      <c r="BH52" s="3">
+        <v>3467</v>
+      </c>
+      <c r="BI52" s="3">
+        <v>2654</v>
+      </c>
+      <c r="BJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="BK52" s="3">
+        <v>136.78992</v>
+      </c>
+      <c r="BL52" s="3">
+        <v>994</v>
+      </c>
+      <c r="BM52" s="3">
+        <v>0.66148800929151241</v>
+      </c>
+      <c r="BN52" s="3">
+        <v>0.86517396241401789</v>
+      </c>
+      <c r="BO52" s="3">
+        <v>0.40319809981627641</v>
+      </c>
+      <c r="BP52" s="3">
+        <v>0.23701266544345051</v>
+      </c>
+      <c r="BQ52" s="3">
+        <v>147.6628323175556</v>
+      </c>
+      <c r="BR52" s="3">
+        <v>193.78571589006521</v>
+      </c>
+      <c r="BS52" s="3">
+        <v>3878.6924665836391</v>
+      </c>
+      <c r="BT52" s="3">
+        <v>302.39736405763318</v>
+      </c>
+      <c r="BU52" s="3">
+        <v>215.08820353509219</v>
+      </c>
+      <c r="BV52" s="3">
+        <v>354.71690799552022</v>
+      </c>
+      <c r="BW52" s="3">
+        <v>2045.989750255668</v>
+      </c>
+      <c r="BX52" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="BY52" s="3">
+        <v>87.5</v>
+      </c>
+      <c r="BZ52" s="3">
+        <v>209.98109438004749</v>
       </c>
     </row>
     <row r="53" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B53" s="4">
         <v>692056</v>
@@ -14764,39 +15417,221 @@
         <v>61</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O53" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="L53" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O53" s="7" t="str">
-        <f>IF(ISNUMBER(MATCH(A53, tableau_floristique!B$1:AJ$1, 0)), "OUI","NON")</f>
-        <v>OUI</v>
+      <c r="Q53">
+        <v>0.12987000000000001</v>
+      </c>
+      <c r="R53" s="3">
+        <v>1</v>
+      </c>
+      <c r="S53" s="3">
+        <v>3.3376600000000001</v>
+      </c>
+      <c r="T53" s="3">
+        <v>45</v>
+      </c>
+      <c r="U53" s="3">
+        <v>95</v>
+      </c>
+      <c r="V53" s="3">
+        <v>100</v>
+      </c>
+      <c r="W53" s="3">
+        <v>78</v>
+      </c>
+      <c r="X53" s="3">
+        <v>104</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>92</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>4</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>43</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>46</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>28</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>52</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>44</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>86</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>150</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>158</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>137</v>
+      </c>
+      <c r="AJ53" s="3">
+        <v>161</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>142</v>
+      </c>
+      <c r="AL53" s="3">
+        <v>508</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>508</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>304</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>348</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>412</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>508</v>
+      </c>
+      <c r="AR53" s="3">
+        <v>214</v>
+      </c>
+      <c r="AS53" s="3">
+        <v>804</v>
+      </c>
+      <c r="AT53" s="3">
+        <v>829</v>
+      </c>
+      <c r="AU53" s="3">
+        <v>714</v>
+      </c>
+      <c r="AV53" s="3">
+        <v>852</v>
+      </c>
+      <c r="AW53" s="3">
+        <v>740</v>
+      </c>
+      <c r="AX53" s="3">
+        <v>711</v>
+      </c>
+      <c r="AY53" s="3">
+        <v>352</v>
+      </c>
+      <c r="AZ53" s="3">
+        <v>-428</v>
+      </c>
+      <c r="BA53" s="3">
+        <v>-78</v>
+      </c>
+      <c r="BB53" s="3">
+        <v>-47</v>
+      </c>
+      <c r="BC53" s="3">
+        <v>449</v>
+      </c>
+      <c r="BD53" s="3">
+        <v>3454</v>
+      </c>
+      <c r="BE53" s="3">
+        <v>1196</v>
+      </c>
+      <c r="BF53" s="3">
+        <v>1904</v>
+      </c>
+      <c r="BG53" s="3">
+        <v>2411</v>
+      </c>
+      <c r="BH53" s="3">
+        <v>3575</v>
+      </c>
+      <c r="BI53" s="3">
+        <v>2770</v>
+      </c>
+      <c r="BJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="BK53" s="3">
+        <v>307.875</v>
+      </c>
+      <c r="BL53" s="3">
+        <v>893</v>
+      </c>
+      <c r="BM53" s="3">
+        <v>0.33481980851124699</v>
+      </c>
+      <c r="BN53" s="3">
+        <v>0.55376877223481491</v>
+      </c>
+      <c r="BO53" s="3">
+        <v>0.63479107940483104</v>
+      </c>
+      <c r="BP53" s="3">
+        <v>0.40687308714125342</v>
+      </c>
+      <c r="BQ53" s="3">
+        <v>1304.0849358838971</v>
+      </c>
+      <c r="BR53" s="3">
+        <v>382.71614807830531</v>
+      </c>
+      <c r="BS53" s="3">
+        <v>401.46893708370152</v>
+      </c>
+      <c r="BT53" s="3">
+        <v>351.44572838663589</v>
+      </c>
+      <c r="BU53" s="3">
+        <v>351.33990664300268</v>
+      </c>
+      <c r="BW53" s="3">
+        <v>2476.066357784779</v>
+      </c>
+      <c r="BX53" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="BY53" s="3">
+        <v>61.25</v>
+      </c>
+      <c r="BZ53" s="3">
+        <v>337.57643664787253</v>
       </c>
     </row>
     <row r="54" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B54" s="4">
         <v>694459.45</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="3">
         <v>6385708.8899999997</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -14809,43 +15644,228 @@
         <v>50</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O54" s="7" t="str">
-        <f>IF(ISNUMBER(MATCH(A54, tableau_floristique!B$1:AJ$1, 0)), "OUI","NON")</f>
-        <v>NON</v>
+        <v>80</v>
+      </c>
+      <c r="O54" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q54">
+        <v>0.12987000000000001</v>
+      </c>
+      <c r="R54" s="3">
+        <v>1</v>
+      </c>
+      <c r="S54" s="3">
+        <v>3.3376600000000001</v>
+      </c>
+      <c r="T54" s="3">
+        <v>38</v>
+      </c>
+      <c r="U54" s="3">
+        <v>83</v>
+      </c>
+      <c r="V54" s="3">
+        <v>89</v>
+      </c>
+      <c r="W54" s="3">
+        <v>66</v>
+      </c>
+      <c r="X54" s="3">
+        <v>91</v>
+      </c>
+      <c r="Y54" s="3">
+        <v>79</v>
+      </c>
+      <c r="Z54" s="3">
+        <v>8</v>
+      </c>
+      <c r="AA54" s="3">
+        <v>43</v>
+      </c>
+      <c r="AB54" s="3">
+        <v>50</v>
+      </c>
+      <c r="AC54" s="3">
+        <v>25</v>
+      </c>
+      <c r="AD54" s="3">
+        <v>48</v>
+      </c>
+      <c r="AE54" s="3">
+        <v>43</v>
+      </c>
+      <c r="AF54" s="3">
+        <v>70</v>
+      </c>
+      <c r="AG54" s="3">
+        <v>125</v>
+      </c>
+      <c r="AH54" s="3">
+        <v>134</v>
+      </c>
+      <c r="AI54" s="3">
+        <v>111</v>
+      </c>
+      <c r="AJ54" s="3">
+        <v>137</v>
+      </c>
+      <c r="AK54" s="3">
+        <v>117</v>
+      </c>
+      <c r="AL54" s="3">
+        <v>659</v>
+      </c>
+      <c r="AM54" s="3">
+        <v>659</v>
+      </c>
+      <c r="AN54" s="3">
+        <v>446</v>
+      </c>
+      <c r="AO54" s="3">
+        <v>535</v>
+      </c>
+      <c r="AP54" s="3">
+        <v>551</v>
+      </c>
+      <c r="AQ54" s="3">
+        <v>659</v>
+      </c>
+      <c r="AR54" s="3">
+        <v>194</v>
+      </c>
+      <c r="AS54" s="3">
+        <v>769</v>
+      </c>
+      <c r="AT54" s="3">
+        <v>800</v>
+      </c>
+      <c r="AU54" s="3">
+        <v>661</v>
+      </c>
+      <c r="AV54" s="3">
+        <v>833</v>
+      </c>
+      <c r="AW54" s="3">
+        <v>699</v>
+      </c>
+      <c r="AX54" s="3">
+        <v>711</v>
+      </c>
+      <c r="AY54" s="3">
+        <v>370</v>
+      </c>
+      <c r="AZ54" s="3">
+        <v>-415</v>
+      </c>
+      <c r="BA54" s="3">
+        <v>-36</v>
+      </c>
+      <c r="BB54" s="3">
+        <v>-48</v>
+      </c>
+      <c r="BC54" s="3">
+        <v>476</v>
+      </c>
+      <c r="BD54" s="3">
+        <v>3439</v>
+      </c>
+      <c r="BE54" s="3">
+        <v>1161</v>
+      </c>
+      <c r="BF54" s="3">
+        <v>1876</v>
+      </c>
+      <c r="BG54" s="3">
+        <v>2364</v>
+      </c>
+      <c r="BH54" s="3">
+        <v>3523</v>
+      </c>
+      <c r="BI54" s="3">
+        <v>2725</v>
+      </c>
+      <c r="BJ54" s="3">
+        <v>0</v>
+      </c>
+      <c r="BK54" s="3">
+        <v>279.46233999999998</v>
+      </c>
+      <c r="BL54" s="3">
+        <v>965</v>
+      </c>
+      <c r="BM54" s="3">
+        <v>7.4105804545835288E-3</v>
+      </c>
+      <c r="BN54" s="3">
+        <v>9.3885444667137677E-2</v>
+      </c>
+      <c r="BO54" s="3">
+        <v>0.92840538941782447</v>
+      </c>
+      <c r="BP54" s="3">
+        <v>0.8696831830821814</v>
+      </c>
+      <c r="BQ54" s="3">
+        <v>234.29811480247841</v>
+      </c>
+      <c r="BR54" s="3">
+        <v>112.1489661120001</v>
+      </c>
+      <c r="BS54" s="3">
+        <v>1252.1556034125169</v>
+      </c>
+      <c r="BT54" s="3">
+        <v>233.3540798876131</v>
+      </c>
+      <c r="BU54" s="3">
+        <v>112.4752177147361</v>
+      </c>
+      <c r="BV54" s="3">
+        <v>2666.6679541086778</v>
+      </c>
+      <c r="BW54" s="3">
+        <v>7794.6334685361944</v>
+      </c>
+      <c r="BX54" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="BY54" s="3">
+        <v>81.176019996774698</v>
+      </c>
+      <c r="BZ54" s="3">
+        <v>1147.642516301963</v>
       </c>
     </row>
     <row r="55" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B55" s="4">
+        <v>210</v>
+      </c>
+      <c r="B55" s="3">
         <v>697391.72</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="3">
         <v>6390262.3799999999</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>27</v>
@@ -14854,39 +15874,224 @@
         <v>63</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q55">
+        <v>0.12987000000000001</v>
+      </c>
+      <c r="R55" s="3">
+        <v>1</v>
+      </c>
+      <c r="S55" s="3">
+        <v>3.3376600000000001</v>
+      </c>
+      <c r="T55" s="3">
+        <v>31</v>
+      </c>
+      <c r="U55" s="3">
+        <v>74</v>
+      </c>
+      <c r="V55" s="3">
         <v>81</v>
       </c>
-      <c r="J55" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O55" s="7" t="str">
-        <f>IF(ISNUMBER(MATCH(A55, tableau_floristique!B$1:AJ$1, 0)), "OUI","NON")</f>
-        <v>NON</v>
+      <c r="W55" s="3">
+        <v>58</v>
+      </c>
+      <c r="X55" s="3">
+        <v>85</v>
+      </c>
+      <c r="Y55" s="3">
+        <v>71</v>
+      </c>
+      <c r="Z55" s="3">
+        <v>-11</v>
+      </c>
+      <c r="AA55" s="3">
+        <v>24</v>
+      </c>
+      <c r="AB55" s="3">
+        <v>28</v>
+      </c>
+      <c r="AC55" s="3">
+        <v>4</v>
+      </c>
+      <c r="AD55" s="3">
+        <v>29</v>
+      </c>
+      <c r="AE55" s="3">
+        <v>26</v>
+      </c>
+      <c r="AF55" s="3">
+        <v>73</v>
+      </c>
+      <c r="AG55" s="3">
+        <v>122</v>
+      </c>
+      <c r="AH55" s="3">
+        <v>131</v>
+      </c>
+      <c r="AI55" s="3">
+        <v>110</v>
+      </c>
+      <c r="AJ55" s="3">
+        <v>140</v>
+      </c>
+      <c r="AK55" s="3">
+        <v>115</v>
+      </c>
+      <c r="AL55" s="3">
+        <v>573</v>
+      </c>
+      <c r="AM55" s="3">
+        <v>573</v>
+      </c>
+      <c r="AN55" s="3">
+        <v>395</v>
+      </c>
+      <c r="AO55" s="3">
+        <v>502</v>
+      </c>
+      <c r="AP55" s="3">
+        <v>472</v>
+      </c>
+      <c r="AQ55" s="3">
+        <v>573</v>
+      </c>
+      <c r="AR55" s="3">
+        <v>169</v>
+      </c>
+      <c r="AS55" s="3">
+        <v>718</v>
+      </c>
+      <c r="AT55" s="3">
+        <v>759</v>
+      </c>
+      <c r="AU55" s="3">
+        <v>607</v>
+      </c>
+      <c r="AV55" s="3">
+        <v>800</v>
+      </c>
+      <c r="AW55" s="3">
+        <v>651</v>
+      </c>
+      <c r="AX55" s="3">
+        <v>713</v>
+      </c>
+      <c r="AY55" s="3">
+        <v>362</v>
+      </c>
+      <c r="AZ55" s="3">
+        <v>-379</v>
+      </c>
+      <c r="BA55" s="3">
+        <v>10</v>
+      </c>
+      <c r="BB55" s="3">
+        <v>-19</v>
+      </c>
+      <c r="BC55" s="3">
+        <v>537</v>
+      </c>
+      <c r="BD55" s="3">
+        <v>3250</v>
+      </c>
+      <c r="BE55" s="3">
+        <v>1148</v>
+      </c>
+      <c r="BF55" s="3">
+        <v>1858</v>
+      </c>
+      <c r="BG55" s="3">
+        <v>2359</v>
+      </c>
+      <c r="BH55" s="3">
+        <v>3582</v>
+      </c>
+      <c r="BI55" s="3">
+        <v>2658</v>
+      </c>
+      <c r="BJ55" s="3">
+        <v>0</v>
+      </c>
+      <c r="BK55" s="3">
+        <v>201.80141</v>
+      </c>
+      <c r="BL55" s="3">
+        <v>1138</v>
+      </c>
+      <c r="BM55" s="3">
+        <v>0.55814515871830339</v>
+      </c>
+      <c r="BN55" s="3">
+        <v>0.55144626799787688</v>
+      </c>
+      <c r="BO55" s="3">
+        <v>0.45920574542290382</v>
+      </c>
+      <c r="BP55" s="3">
+        <v>0.44055637205797848</v>
+      </c>
+      <c r="BQ55" s="3">
+        <v>88.617418152562678</v>
+      </c>
+      <c r="BR55" s="3">
+        <v>704.4562527941597</v>
+      </c>
+      <c r="BS55" s="3">
+        <v>199.91152979606289</v>
+      </c>
+      <c r="BT55" s="3">
+        <v>37.909732308032297</v>
+      </c>
+      <c r="BU55" s="3">
+        <v>42.265243404163087</v>
+      </c>
+      <c r="BV55" s="3">
+        <v>283.47343880496919</v>
+      </c>
+      <c r="BW55" s="3">
+        <v>808.11576718010474</v>
+      </c>
+      <c r="BX55" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="BY55" s="3">
+        <v>73.375</v>
+      </c>
+      <c r="BZ55" s="3">
+        <v>831.54528720477924</v>
       </c>
     </row>
     <row r="56" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B56" s="4">
         <v>696138</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="3">
         <v>6383359</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -14896,32 +16101,217 @@
         <v>21</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>65</v>
+        <v>395</v>
       </c>
       <c r="H56" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="O56" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q56">
+        <v>0.64295000000000002</v>
+      </c>
+      <c r="R56" s="3">
+        <v>0.81440000000000001</v>
+      </c>
+      <c r="S56" s="3">
+        <v>2.2074600000000002</v>
+      </c>
+      <c r="T56" s="3">
+        <v>40</v>
+      </c>
+      <c r="U56" s="3">
+        <v>86</v>
+      </c>
+      <c r="V56" s="3">
+        <v>92</v>
+      </c>
+      <c r="W56" s="3">
+        <v>69</v>
+      </c>
+      <c r="X56" s="3">
+        <v>95</v>
+      </c>
+      <c r="Y56" s="3">
         <v>82</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="O56" s="7" t="str">
-        <f>IF(ISNUMBER(MATCH(A56, tableau_floristique!B$1:AJ$1, 0)), "OUI","NON")</f>
-        <v>OUI</v>
+      <c r="Z56" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA56" s="3">
+        <v>45</v>
+      </c>
+      <c r="AB56" s="3">
+        <v>52</v>
+      </c>
+      <c r="AC56" s="3">
+        <v>27</v>
+      </c>
+      <c r="AD56" s="3">
+        <v>50</v>
+      </c>
+      <c r="AE56" s="3">
+        <v>46</v>
+      </c>
+      <c r="AF56" s="3">
+        <v>72</v>
+      </c>
+      <c r="AG56" s="3">
+        <v>127</v>
+      </c>
+      <c r="AH56" s="3">
+        <v>136</v>
+      </c>
+      <c r="AI56" s="3">
+        <v>113</v>
+      </c>
+      <c r="AJ56" s="3">
+        <v>139</v>
+      </c>
+      <c r="AK56" s="3">
+        <v>120</v>
+      </c>
+      <c r="AL56" s="3">
+        <v>592</v>
+      </c>
+      <c r="AM56" s="3">
+        <v>592</v>
+      </c>
+      <c r="AN56" s="3">
+        <v>367</v>
+      </c>
+      <c r="AO56" s="3">
+        <v>437</v>
+      </c>
+      <c r="AP56" s="3">
+        <v>473</v>
+      </c>
+      <c r="AQ56" s="3">
+        <v>592</v>
+      </c>
+      <c r="AR56" s="3">
+        <v>201</v>
+      </c>
+      <c r="AS56" s="3">
+        <v>777</v>
+      </c>
+      <c r="AT56" s="3">
+        <v>809</v>
+      </c>
+      <c r="AU56" s="3">
+        <v>678</v>
+      </c>
+      <c r="AV56" s="3">
+        <v>846</v>
+      </c>
+      <c r="AW56" s="3">
+        <v>711</v>
+      </c>
+      <c r="AX56" s="3">
+        <v>693</v>
+      </c>
+      <c r="AY56" s="3">
+        <v>379</v>
+      </c>
+      <c r="AZ56" s="3">
+        <v>-438</v>
+      </c>
+      <c r="BA56" s="3">
+        <v>-63</v>
+      </c>
+      <c r="BB56" s="3">
+        <v>-82</v>
+      </c>
+      <c r="BC56" s="3">
+        <v>436</v>
+      </c>
+      <c r="BD56" s="3">
+        <v>3465</v>
+      </c>
+      <c r="BE56" s="3">
+        <v>1122</v>
+      </c>
+      <c r="BF56" s="3">
+        <v>1852</v>
+      </c>
+      <c r="BG56" s="3">
+        <v>2308</v>
+      </c>
+      <c r="BH56" s="3">
+        <v>3457</v>
+      </c>
+      <c r="BI56" s="3">
+        <v>2692</v>
+      </c>
+      <c r="BJ56" s="3">
+        <v>0</v>
+      </c>
+      <c r="BK56" s="3">
+        <v>327.80426</v>
+      </c>
+      <c r="BL56" s="3">
+        <v>979</v>
+      </c>
+      <c r="BM56" s="3">
+        <v>0.35871701417253249</v>
+      </c>
+      <c r="BN56" s="3">
+        <v>0.35400369202426851</v>
+      </c>
+      <c r="BO56" s="3">
+        <v>0.64713797585570465</v>
+      </c>
+      <c r="BP56" s="3">
+        <v>0.63796001613258646</v>
+      </c>
+      <c r="BQ56" s="3">
+        <v>478.53870271915071</v>
+      </c>
+      <c r="BR56" s="3">
+        <v>279.74558663895829</v>
+      </c>
+      <c r="BS56" s="3">
+        <v>4124.4229684089796</v>
+      </c>
+      <c r="BT56" s="3">
+        <v>312.50789392276653</v>
+      </c>
+      <c r="BU56" s="3">
+        <v>245.9738603996785</v>
+      </c>
+      <c r="BV56" s="3">
+        <v>2.528139504604042</v>
+      </c>
+      <c r="BW56" s="3">
+        <v>67.749553993344307</v>
+      </c>
+      <c r="BX56" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="BY56" s="3">
+        <v>69.316088840736697</v>
+      </c>
+      <c r="BZ56" s="3">
+        <v>395.18027778863848</v>
       </c>
     </row>
   </sheetData>
@@ -14951,117 +16341,117 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="AC1" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AD1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="AF1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="AE1" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF1" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="AG1" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
@@ -15171,7 +16561,7 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B3" s="4">
         <v>0</v>
@@ -15281,7 +16671,7 @@
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B4" s="4">
         <v>0</v>
@@ -15391,7 +16781,7 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B5" s="4">
         <v>0</v>
@@ -15501,7 +16891,7 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B6" s="4">
         <v>0</v>
@@ -15611,7 +17001,7 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B7" s="4">
         <v>0.5</v>
@@ -15721,7 +17111,7 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B8" s="4">
         <v>0.5</v>
@@ -15831,7 +17221,7 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B9" s="4">
         <v>0</v>
@@ -15941,7 +17331,7 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B10" s="4">
         <v>0</v>
@@ -16051,7 +17441,7 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B11" s="4">
         <v>0.5</v>
@@ -16161,7 +17551,7 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12" s="4">
         <v>0</v>
@@ -16271,7 +17661,7 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B13" s="4">
         <v>0</v>
@@ -16381,7 +17771,7 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B14" s="4">
         <v>0</v>
@@ -16491,7 +17881,7 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B15" s="4">
         <v>0</v>
@@ -16601,7 +17991,7 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
@@ -16711,7 +18101,7 @@
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B17" s="4">
         <v>0.5</v>
@@ -16821,7 +18211,7 @@
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B18" s="4">
         <v>0</v>
@@ -16931,7 +18321,7 @@
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B19" s="4">
         <v>0</v>
@@ -17041,7 +18431,7 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B20" s="4">
         <v>0.5</v>
@@ -17151,7 +18541,7 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B21" s="4">
         <v>0.5</v>
@@ -17261,7 +18651,7 @@
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B22" s="4">
         <v>0</v>
@@ -17371,7 +18761,7 @@
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B23" s="4">
         <v>0</v>
@@ -17481,7 +18871,7 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B24" s="4">
         <v>0</v>
@@ -17591,7 +18981,7 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B25" s="4">
         <v>0</v>
@@ -17701,7 +19091,7 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B26" s="4">
         <v>0</v>
@@ -17811,7 +19201,7 @@
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B27" s="4">
         <v>0</v>
@@ -17921,7 +19311,7 @@
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B28" s="4">
         <v>0.5</v>
@@ -18031,7 +19421,7 @@
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B29" s="4">
         <v>0</v>
@@ -18141,7 +19531,7 @@
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B30" s="4">
         <v>0</v>
@@ -18251,7 +19641,7 @@
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B31" s="4">
         <v>0</v>
@@ -18361,7 +19751,7 @@
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B32" s="4">
         <v>2</v>
@@ -18471,7 +19861,7 @@
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B33" s="4">
         <v>0</v>
@@ -18581,7 +19971,7 @@
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B34" s="4">
         <v>0.5</v>
@@ -18691,7 +20081,7 @@
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B35" s="4">
         <v>0</v>
@@ -18801,7 +20191,7 @@
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B36" s="4">
         <v>2</v>
@@ -18911,7 +20301,7 @@
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B37" s="4">
         <v>0</v>
@@ -19021,7 +20411,7 @@
     </row>
     <row r="38" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B38" s="4">
         <v>0</v>
@@ -19131,7 +20521,7 @@
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B39" s="4">
         <v>1</v>
@@ -19242,7 +20632,7 @@
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B40" s="4">
         <v>0</v>
@@ -19352,7 +20742,7 @@
     </row>
     <row r="41" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B41" s="4">
         <v>0</v>
@@ -19462,7 +20852,7 @@
     </row>
     <row r="42" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B42" s="4">
         <v>1</v>
@@ -19572,7 +20962,7 @@
     </row>
     <row r="43" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B43" s="4">
         <v>0</v>
@@ -19682,7 +21072,7 @@
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B44" s="4">
         <v>0</v>
@@ -19792,7 +21182,7 @@
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B45" s="4">
         <v>0</v>
@@ -19902,7 +21292,7 @@
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B46" s="4">
         <v>1</v>
@@ -20012,7 +21402,7 @@
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B47" s="4">
         <v>0</v>
@@ -20122,7 +21512,7 @@
     </row>
     <row r="48" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B48" s="4">
         <v>0</v>
@@ -20232,7 +21622,7 @@
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" s="4">
         <v>1</v>
@@ -20342,7 +21732,7 @@
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B50" s="4">
         <v>0.5</v>
@@ -20452,7 +21842,7 @@
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B51" s="4">
         <v>0</v>
@@ -20562,7 +21952,7 @@
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B52" s="4">
         <v>0.5</v>
@@ -20672,7 +22062,7 @@
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B53" s="4">
         <v>0</v>
@@ -20782,7 +22172,7 @@
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B54" s="4">
         <v>0</v>
@@ -20892,7 +22282,7 @@
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B55" s="4">
         <v>0</v>
@@ -21002,7 +22392,7 @@
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B56" s="4">
         <v>0</v>
@@ -21112,7 +22502,7 @@
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B57" s="4">
         <v>0</v>
@@ -21222,7 +22612,7 @@
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B58" s="4">
         <v>3</v>
@@ -21332,7 +22722,7 @@
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B59" s="4">
         <v>0</v>
@@ -21442,7 +22832,7 @@
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B60" s="4">
         <v>0.5</v>
@@ -21552,7 +22942,7 @@
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B61" s="4">
         <v>0</v>
@@ -21662,7 +23052,7 @@
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B62" s="4">
         <v>0</v>
@@ -21772,7 +23162,7 @@
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B63" s="4">
         <v>0</v>
@@ -21882,7 +23272,7 @@
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B64" s="4">
         <v>0</v>
@@ -21992,7 +23382,7 @@
     </row>
     <row r="65" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B65" s="4">
         <v>0</v>
@@ -22102,7 +23492,7 @@
     </row>
     <row r="66" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B66" s="4">
         <v>0.5</v>
@@ -22212,7 +23602,7 @@
     </row>
     <row r="67" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B67" s="4">
         <v>0</v>
@@ -22322,7 +23712,7 @@
     </row>
     <row r="68" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B68" s="4">
         <v>0</v>
@@ -22432,7 +23822,7 @@
     </row>
     <row r="69" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B69" s="4">
         <v>0</v>
@@ -22542,7 +23932,7 @@
     </row>
     <row r="70" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B70" s="4">
         <v>0</v>
@@ -22652,7 +24042,7 @@
     </row>
     <row r="71" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B71" s="4">
         <v>0</v>
@@ -22762,7 +24152,7 @@
     </row>
     <row r="72" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B72" s="4">
         <v>1</v>
@@ -22872,7 +24262,7 @@
     </row>
     <row r="73" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B73" s="4">
         <v>0</v>
@@ -22982,7 +24372,7 @@
     </row>
     <row r="74" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B74" s="4">
         <v>2</v>
@@ -23092,7 +24482,7 @@
     </row>
     <row r="75" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B75" s="4">
         <v>0</v>
@@ -23202,7 +24592,7 @@
     </row>
     <row r="76" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B76" s="4">
         <v>0</v>
@@ -23312,7 +24702,7 @@
     </row>
     <row r="77" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B77" s="8">
         <v>0</v>
@@ -23422,7 +24812,7 @@
     </row>
     <row r="78" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B78" s="4">
         <v>0</v>
@@ -23532,7 +24922,7 @@
     </row>
     <row r="79" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B79" s="4">
         <v>0.5</v>
@@ -23642,7 +25032,7 @@
     </row>
     <row r="80" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B80" s="4">
         <v>2</v>
@@ -23752,7 +25142,7 @@
     </row>
     <row r="81" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B81" s="4">
         <v>0</v>
@@ -23862,7 +25252,7 @@
     </row>
     <row r="82" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B82" s="4">
         <v>0.5</v>
@@ -23972,7 +25362,7 @@
     </row>
     <row r="83" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B83" s="4">
         <v>0</v>
@@ -24082,7 +25472,7 @@
     </row>
     <row r="84" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B84" s="4">
         <v>1</v>
@@ -24192,7 +25582,7 @@
     </row>
     <row r="85" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B85" s="4">
         <v>0</v>
@@ -24302,7 +25692,7 @@
     </row>
     <row r="86" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B86" s="4">
         <v>0.5</v>
@@ -24412,7 +25802,7 @@
     </row>
     <row r="87" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B87" s="4">
         <v>0</v>
@@ -24522,7 +25912,7 @@
     </row>
     <row r="88" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B88" s="4">
         <v>0</v>
@@ -24632,7 +26022,7 @@
     </row>
     <row r="89" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B89" s="4">
         <v>0</v>
@@ -24742,7 +26132,7 @@
     </row>
     <row r="90" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B90" s="4">
         <v>0</v>
@@ -24852,7 +26242,7 @@
     </row>
     <row r="91" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B91" s="4">
         <v>0</v>
@@ -24962,7 +26352,7 @@
     </row>
     <row r="92" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B92" s="4">
         <v>0</v>
@@ -25072,7 +26462,7 @@
     </row>
     <row r="93" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B93" s="4">
         <v>0</v>
@@ -25182,7 +26572,7 @@
     </row>
     <row r="94" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B94" s="4">
         <v>0</v>
@@ -25292,7 +26682,7 @@
     </row>
     <row r="95" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B95" s="4">
         <v>0</v>
@@ -25402,7 +26792,7 @@
     </row>
     <row r="96" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B96" s="4">
         <v>0</v>
@@ -25512,7 +26902,7 @@
     </row>
     <row r="97" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B97" s="4">
         <v>0</v>
@@ -25622,7 +27012,7 @@
     </row>
     <row r="98" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B98" s="4">
         <v>0</v>
@@ -25732,7 +27122,7 @@
     </row>
     <row r="99" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B99" s="4">
         <v>0.5</v>
@@ -25842,7 +27232,7 @@
     </row>
     <row r="100" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B100" s="4">
         <v>0</v>
@@ -25952,7 +27342,7 @@
     </row>
     <row r="101" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B101" s="4">
         <v>0</v>
@@ -26062,7 +27452,7 @@
     </row>
     <row r="102" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B102" s="4">
         <v>0</v>
@@ -26172,7 +27562,7 @@
     </row>
     <row r="103" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B103" s="4">
         <v>1</v>
@@ -26282,7 +27672,7 @@
     </row>
     <row r="104" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B104" s="4">
         <v>2</v>
@@ -26392,7 +27782,7 @@
     </row>
     <row r="105" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B105" s="4">
         <v>0</v>
@@ -26502,7 +27892,7 @@
     </row>
     <row r="106" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B106" s="4">
         <v>0</v>
@@ -26612,7 +28002,7 @@
     </row>
     <row r="107" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B107" s="4">
         <v>0</v>
@@ -26722,7 +28112,7 @@
     </row>
     <row r="108" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B108" s="4">
         <v>0</v>
@@ -26832,7 +28222,7 @@
     </row>
     <row r="109" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B109" s="4">
         <v>0.5</v>
@@ -26942,7 +28332,7 @@
     </row>
     <row r="110" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B110" s="4">
         <v>0</v>
@@ -27052,7 +28442,7 @@
     </row>
     <row r="111" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B111" s="4">
         <v>0</v>
@@ -27162,7 +28552,7 @@
     </row>
     <row r="112" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B112" s="4">
         <v>0</v>
@@ -27272,7 +28662,7 @@
     </row>
     <row r="113" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B113" s="8">
         <v>0.5</v>
@@ -27382,7 +28772,7 @@
     </row>
     <row r="114" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B114" s="4">
         <v>0</v>
@@ -27492,7 +28882,7 @@
     </row>
     <row r="115" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B115" s="4">
         <v>0</v>
@@ -27622,30 +29012,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
         <v>66</v>
-      </c>
-      <c r="D1" t="s">
-        <v>67</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" t="s">
         <v>68</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>69</v>
-      </c>
-      <c r="H1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" s="1">
         <v>43915</v>
@@ -27672,7 +29062,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="1">
         <v>44232</v>
@@ -27699,7 +29089,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4" s="1">
         <v>44607</v>
@@ -27726,7 +29116,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5">
@@ -27748,7 +29138,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B6" s="1">
         <v>45352</v>
@@ -27775,7 +29165,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B7" s="1">
         <v>45712</v>
@@ -27802,7 +29192,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B8" s="1">
         <v>46087</v>
@@ -27829,7 +29219,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9">
@@ -27851,7 +29241,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B10" s="1">
         <v>45371</v>
@@ -27878,7 +29268,7 @@
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B11" s="1">
         <v>46097</v>
@@ -27905,7 +29295,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B12" s="1">
         <v>43920</v>
@@ -27932,7 +29322,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B13" s="1">
         <v>44245</v>
@@ -27959,7 +29349,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14">
@@ -27981,7 +29371,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B15" s="1">
         <v>45345</v>
@@ -28008,7 +29398,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B16" s="1">
         <v>45716</v>
@@ -28035,7 +29425,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B17" s="1">
         <v>43922</v>
@@ -28062,7 +29452,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B18" s="1">
         <v>44240</v>
@@ -28089,7 +29479,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B19" s="1">
         <v>44605</v>
@@ -28116,7 +29506,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20">
@@ -28138,7 +29528,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B21" s="1">
         <v>45342</v>
@@ -28165,7 +29555,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" s="1">
         <v>45705</v>
@@ -28192,7 +29582,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B23" s="1">
         <v>46082</v>
@@ -28219,7 +29609,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24">
@@ -28241,7 +29631,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B25" s="1">
         <v>45355</v>
@@ -28268,7 +29658,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B26" s="1">
         <v>45711</v>
@@ -28295,7 +29685,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B27" s="1">
         <v>46083</v>
@@ -28322,7 +29712,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B28" s="1">
         <v>43915</v>
@@ -28349,7 +29739,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B29" s="1">
         <v>44244</v>
@@ -28376,7 +29766,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B30" s="1">
         <v>44653</v>
@@ -28403,7 +29793,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31">
@@ -28425,7 +29815,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B32" s="1">
         <v>43915</v>
@@ -28452,7 +29842,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B33" s="1">
         <v>44241</v>
@@ -28479,7 +29869,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B34" s="1">
         <v>44602</v>
@@ -28506,7 +29896,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35">
@@ -28528,7 +29918,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B36" s="1">
         <v>45339</v>
@@ -28555,7 +29945,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B37" s="1">
         <v>45705</v>
@@ -28582,7 +29972,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B38" s="1">
         <v>46071</v>
@@ -28609,7 +29999,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B39" s="1">
         <v>43915</v>
@@ -28636,7 +30026,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B40" s="1">
         <v>44238</v>
@@ -28663,7 +30053,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B41" s="1">
         <v>44607</v>
@@ -28690,7 +30080,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42">
@@ -28712,7 +30102,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B43" s="1">
         <v>45348</v>
@@ -28739,7 +30129,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="1">
         <v>45719</v>
@@ -28766,7 +30156,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B45" s="1">
         <v>46081</v>
@@ -28793,7 +30183,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46">
@@ -28815,7 +30205,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B47" s="1">
         <v>45348</v>
@@ -28842,7 +30232,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48">
@@ -28862,7 +30252,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B49" s="1">
         <v>45713</v>
@@ -28889,7 +30279,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B50" s="1">
         <v>46081</v>
@@ -28916,7 +30306,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51">
@@ -28938,7 +30328,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B52" s="1">
         <v>45356</v>
@@ -28965,7 +30355,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B53" s="1">
         <v>45718</v>
@@ -28992,7 +30382,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B54" s="1">
         <v>46083</v>
@@ -29019,7 +30409,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B55" s="1">
         <v>43922</v>
@@ -29046,7 +30436,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B56" s="1">
         <v>44232</v>
@@ -29073,7 +30463,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B57" s="1">
         <v>44607</v>
@@ -29100,7 +30490,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B58" s="1"/>
       <c r="C58">
@@ -29122,7 +30512,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B59" s="1">
         <v>45337</v>
@@ -29149,7 +30539,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B60" s="1">
         <v>45698</v>
@@ -29176,7 +30566,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B61" s="1">
         <v>46070</v>
@@ -29203,7 +30593,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62">
@@ -29225,7 +30615,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>362</v>
       </c>
       <c r="B63" s="1">
         <v>43915</v>
@@ -29252,7 +30642,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>165</v>
+        <v>362</v>
       </c>
       <c r="B64" s="1">
         <v>44243</v>
@@ -29279,7 +30669,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>166</v>
+        <v>362</v>
       </c>
       <c r="B65" s="1">
         <v>44674</v>
@@ -29306,7 +30696,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>362</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66">
@@ -29328,7 +30718,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>166</v>
+        <v>362</v>
       </c>
       <c r="B67" s="1">
         <v>45352</v>
@@ -29355,7 +30745,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>166</v>
+        <v>362</v>
       </c>
       <c r="B68" s="1">
         <v>45713</v>
@@ -29382,7 +30772,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>166</v>
+        <v>362</v>
       </c>
       <c r="B69" s="1">
         <v>46078</v>
@@ -29409,7 +30799,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B70" s="1">
         <v>43922</v>
@@ -29436,7 +30826,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B71" s="1">
         <v>44270</v>
@@ -29463,7 +30853,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B72" s="1">
         <v>44635</v>
@@ -29490,7 +30880,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B73" s="1"/>
       <c r="C73">
@@ -29512,7 +30902,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B74" s="1">
         <v>45357</v>
@@ -29539,7 +30929,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B75" s="1">
         <v>43922</v>
@@ -29566,7 +30956,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B76" s="1">
         <v>44258</v>
@@ -29593,7 +30983,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B77" s="1">
         <v>44622</v>
@@ -29620,7 +31010,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C78">
         <v>2023</v>
@@ -29642,7 +31032,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B79" s="1">
         <v>45362</v>
@@ -29669,7 +31059,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B80" s="1">
         <v>45741</v>
@@ -29696,7 +31086,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B81" s="1">
         <v>46059</v>
@@ -29723,7 +31113,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B82" s="1">
         <v>44301</v>
@@ -29750,7 +31140,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B83" s="1">
         <v>44661</v>
@@ -29777,7 +31167,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B84" s="1"/>
       <c r="C84">
@@ -29799,7 +31189,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B85" s="1">
         <v>45352</v>
@@ -29826,7 +31216,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B86" s="1">
         <v>45753</v>
@@ -29853,7 +31243,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B87" s="1">
         <v>43915</v>
@@ -29880,7 +31270,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B88" s="1">
         <v>44253</v>
@@ -29907,7 +31297,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B89" s="1">
         <v>44625</v>
@@ -29934,7 +31324,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B90" s="1">
         <v>45356</v>
@@ -29961,7 +31351,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B91" s="1">
         <v>45733</v>
@@ -29988,7 +31378,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B92" s="1">
         <v>46094</v>
@@ -30015,7 +31405,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B93" s="1">
         <v>43915</v>
@@ -30042,7 +31432,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B94" s="1">
         <v>44266</v>
@@ -30069,7 +31459,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B95" s="1">
         <v>44617</v>
@@ -30096,7 +31486,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96">
@@ -30118,7 +31508,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B97" s="1">
         <v>45345</v>
@@ -30145,7 +31535,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B98" s="1">
         <v>45726</v>
@@ -30172,7 +31562,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B99" s="1">
         <v>46091</v>
@@ -30199,7 +31589,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>178</v>
+        <v>372</v>
       </c>
       <c r="B100" s="1">
         <v>43918</v>
@@ -30226,7 +31616,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>178</v>
+        <v>372</v>
       </c>
       <c r="B101" s="1">
         <v>44254</v>
@@ -30253,7 +31643,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>180</v>
+        <v>372</v>
       </c>
       <c r="B102" s="1">
         <v>44619</v>
@@ -30280,7 +31670,7 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>180</v>
+        <v>372</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103">
@@ -30302,7 +31692,7 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>180</v>
+        <v>372</v>
       </c>
       <c r="B104" s="1">
         <v>45325</v>
@@ -30329,7 +31719,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>180</v>
+        <v>372</v>
       </c>
       <c r="B105" s="1">
         <v>45708</v>
@@ -30356,7 +31746,7 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>180</v>
+        <v>372</v>
       </c>
       <c r="B106" s="1">
         <v>46083</v>
@@ -30383,7 +31773,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B107" s="1">
         <v>43922</v>
@@ -30410,7 +31800,7 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B108" s="1">
         <v>44252</v>
@@ -30437,7 +31827,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B109" s="1">
         <v>44659</v>
@@ -30464,7 +31854,7 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B110" s="1"/>
       <c r="C110">
@@ -30486,7 +31876,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B111" s="1">
         <v>45355</v>
@@ -30513,7 +31903,7 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B112" s="1">
         <v>45749</v>
@@ -30540,7 +31930,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B113" s="1">
         <v>46101</v>
@@ -30567,7 +31957,7 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B114" s="1">
         <v>43922</v>
@@ -30594,7 +31984,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B115" s="1"/>
       <c r="C115">
@@ -30616,7 +32006,7 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B116" s="1">
         <v>44635</v>
@@ -30643,7 +32033,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B117" s="1"/>
       <c r="C117">
@@ -30665,7 +32055,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B118" s="1">
         <v>45355</v>
@@ -30692,7 +32082,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B119" s="1">
         <v>45736</v>
@@ -30719,7 +32109,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B120" s="1">
         <v>46093</v>
@@ -30746,7 +32136,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>184</v>
+        <v>376</v>
       </c>
       <c r="B121" s="1">
         <v>43966</v>
@@ -30773,7 +32163,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>184</v>
+        <v>376</v>
       </c>
       <c r="B122" s="1">
         <v>44261</v>
@@ -30800,7 +32190,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>183</v>
+        <v>376</v>
       </c>
       <c r="B123" s="1">
         <v>44614</v>
@@ -30827,7 +32217,7 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>183</v>
+        <v>376</v>
       </c>
       <c r="B124" s="1"/>
       <c r="C124">
@@ -30849,7 +32239,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>183</v>
+        <v>376</v>
       </c>
       <c r="B125" s="1">
         <v>45337</v>
@@ -30876,7 +32266,7 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>183</v>
+        <v>376</v>
       </c>
       <c r="B126" s="1">
         <v>45715</v>
@@ -30903,7 +32293,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>183</v>
+        <v>376</v>
       </c>
       <c r="B127" s="1">
         <v>46073</v>
@@ -30930,7 +32320,7 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B128" s="1">
         <v>43915</v>
@@ -30957,7 +32347,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B129" s="1">
         <v>44280</v>
@@ -30984,7 +32374,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B130" s="1">
         <v>44653</v>
@@ -31011,7 +32401,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131">
@@ -31033,7 +32423,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B132" s="1">
         <v>45368</v>
@@ -31060,7 +32450,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B133" s="1">
         <v>45762</v>
@@ -31087,7 +32477,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B134" s="1">
         <v>46093</v>
@@ -31114,7 +32504,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B135" s="1">
         <v>43915</v>
@@ -31141,7 +32531,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B136" s="1">
         <v>44281</v>
@@ -31168,7 +32558,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B137" s="1">
         <v>44653</v>
@@ -31195,7 +32585,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B138" s="1"/>
       <c r="C138">
@@ -31217,7 +32607,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B139" s="1">
         <v>45741</v>
@@ -31244,7 +32634,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B140" s="1">
         <v>46081</v>
@@ -31271,7 +32661,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B141" s="1">
         <v>43922</v>
@@ -31298,7 +32688,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B142" s="1"/>
       <c r="C142">
@@ -31320,7 +32710,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B143" s="1">
         <v>44621</v>
@@ -31347,7 +32737,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B144" s="1"/>
       <c r="C144">
@@ -31369,7 +32759,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B145" s="1">
         <v>45349</v>
@@ -31396,7 +32786,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B146" s="1">
         <v>44325</v>
@@ -31423,7 +32813,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B147" s="1">
         <v>44635</v>
@@ -31450,7 +32840,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B148" s="1"/>
       <c r="C148">
@@ -31472,7 +32862,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B149" s="1">
         <v>43971</v>
@@ -31499,7 +32889,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B150" s="1">
         <v>44625</v>
@@ -31526,7 +32916,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B151" s="1"/>
       <c r="C151">
@@ -31548,7 +32938,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B152" s="1">
         <v>45355</v>
@@ -31575,7 +32965,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B153" s="1">
         <v>45728</v>
@@ -31602,7 +32992,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B154" s="1">
         <v>46120</v>
@@ -31629,7 +33019,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B155" s="1"/>
       <c r="C155">
@@ -31651,7 +33041,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B156" s="1">
         <v>45355</v>
@@ -31678,7 +33068,7 @@
     </row>
     <row r="157" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B157" s="1">
         <v>45728</v>
@@ -31705,7 +33095,7 @@
     </row>
     <row r="158" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B158" s="1">
         <v>46101</v>
@@ -31732,7 +33122,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B159" s="1">
         <v>43961</v>
@@ -31759,7 +33149,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B160" s="1">
         <v>44287</v>
@@ -31786,7 +33176,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>48</v>
@@ -31813,7 +33203,7 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B162" s="1"/>
       <c r="C162">
@@ -31835,7 +33225,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B163" s="1">
         <v>45384</v>
@@ -31862,7 +33252,7 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B164" s="1">
         <v>45370</v>
@@ -31889,7 +33279,7 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B165" s="1">
         <v>45752</v>
@@ -31916,7 +33306,7 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B166" s="1">
         <v>43982</v>
@@ -31943,7 +33333,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B167" s="1">
         <v>44355</v>
@@ -31970,7 +33360,7 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B168" s="1">
         <v>44713</v>
@@ -31997,7 +33387,7 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B169" s="1"/>
       <c r="C169">
@@ -32019,7 +33409,7 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B170" s="1">
         <v>43946</v>
@@ -32046,7 +33436,7 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B171" s="1">
         <v>44259</v>
@@ -32073,7 +33463,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B172" s="1">
         <v>44603</v>
@@ -32100,7 +33490,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B173" s="1"/>
       <c r="C173">
@@ -32122,7 +33512,7 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B174" s="1">
         <v>45337</v>
@@ -32149,7 +33539,7 @@
     </row>
     <row r="175" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B175" s="1">
         <v>45748</v>
@@ -32176,7 +33566,7 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B176" s="1">
         <v>43922</v>
@@ -32203,7 +33593,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B177" s="1">
         <v>44622</v>
@@ -32230,7 +33620,7 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B178" s="1"/>
       <c r="C178">
@@ -32252,7 +33642,7 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B179" s="1">
         <v>45337</v>
@@ -32279,7 +33669,7 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B180" s="1">
         <v>45747</v>
@@ -32306,7 +33696,7 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B181" s="1">
         <v>46091</v>
@@ -32333,7 +33723,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B182" s="1">
         <v>43922</v>
@@ -32360,7 +33750,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B183" s="1">
         <v>44299</v>
@@ -32387,7 +33777,7 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B184" s="1">
         <v>44622</v>
@@ -32414,7 +33804,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B185" s="1"/>
       <c r="C185">
@@ -32436,7 +33826,7 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B186" s="1">
         <v>45337</v>
@@ -32463,7 +33853,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B187" s="1">
         <v>45748</v>
@@ -32490,7 +33880,7 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B188" s="1">
         <v>46091</v>
@@ -32517,7 +33907,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B189" s="1"/>
       <c r="C189">
@@ -32539,7 +33929,7 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B190" s="1">
         <v>45337</v>
@@ -32566,7 +33956,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B191" s="1">
         <v>45747</v>
@@ -32593,7 +33983,7 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B192" s="1">
         <v>46094</v>
@@ -32620,7 +34010,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B193" s="1">
         <v>43915</v>
@@ -32647,7 +34037,7 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B194" s="1">
         <v>44270</v>
@@ -32674,7 +34064,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B195" s="1">
         <v>44624</v>
@@ -32701,7 +34091,7 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B196" s="1">
         <v>43920</v>
@@ -32728,7 +34118,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B197" s="1"/>
       <c r="C197">
@@ -32750,7 +34140,7 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B198" s="1">
         <v>44624</v>
@@ -32777,7 +34167,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B199" s="1">
         <v>43922</v>
@@ -32804,7 +34194,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B200" s="1">
         <v>43922</v>
@@ -32831,7 +34221,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B201" s="1">
         <v>44291</v>
@@ -32858,7 +34248,7 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B202" s="1">
         <v>44656</v>

--- a/prairies/data/Releves_prairies_biomasse_et_phyto.xlsx
+++ b/prairies/data/Releves_prairies_biomasse_et_phyto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ingé\3A\Stage\Cervides_Aubrac\Analyse\Analyses_Aubrac\prairies\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08129C2C-6BF2-4EFA-8459-527617A30ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B2B63C-A404-494F-BC20-94DFE02CC412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISEZ-MOI" sheetId="13" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">info_points!$A$1:$Q$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">tableau_floristique!$A$1:$AJ$115</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="478">
   <si>
     <t>Id_EE</t>
   </si>
@@ -1476,6 +1476,9 @@
   </si>
   <si>
     <t>Masse fraiche des 6 quadrarts de l'exclos (g)</t>
+  </si>
+  <si>
+    <t>DIST_LISIERE</t>
   </si>
 </sst>
 </file>
@@ -1576,7 +1579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1615,10 +1618,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2341,63 +2340,63 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="B57" s="17" t="s">
+      <c r="A57" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="B57" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="16">
+      <c r="A58" s="13">
         <v>1</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="16">
+      <c r="A59" s="13">
         <v>2</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="16">
+      <c r="A60" s="13">
         <v>3</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="B60" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="16">
+      <c r="A61" s="13">
         <v>4</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="B61" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="16">
+      <c r="A62" s="13">
         <v>5</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="16" t="s">
         <v>468</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="B64" s="17" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="20" t="s">
+      <c r="A65" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B65" t="s">
@@ -2405,7 +2404,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="18" t="s">
         <v>73</v>
       </c>
       <c r="B66" t="s">
@@ -2413,7 +2412,7 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="20" t="s">
+      <c r="A67" s="18" t="s">
         <v>65</v>
       </c>
       <c r="B67" t="s">
@@ -2421,7 +2420,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="20" t="s">
+      <c r="A68" s="18" t="s">
         <v>66</v>
       </c>
       <c r="B68" t="s">
@@ -2429,7 +2428,7 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="20" t="s">
+      <c r="A69" s="18" t="s">
         <v>1</v>
       </c>
       <c r="B69" t="s">
@@ -2437,7 +2436,7 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="20" t="s">
+      <c r="A70" s="18" t="s">
         <v>67</v>
       </c>
       <c r="B70" t="s">
@@ -2445,7 +2444,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="18" t="s">
         <v>68</v>
       </c>
       <c r="B71" t="s">
@@ -2453,7 +2452,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="18" t="s">
         <v>69</v>
       </c>
       <c r="B72" t="s">
@@ -3375,7 +3374,7 @@
   <sheetPr codeName="Feuil3">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:BZ56"/>
+  <dimension ref="A1:CA56"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="3"/>
@@ -3389,7 +3388,7 @@
     <col min="18" max="16384" width="11.42578125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:79" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3624,8 +3623,11 @@
       <c r="BZ1" s="2" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="2" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA1" s="18" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="2" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>160</v>
       </c>
@@ -3854,8 +3856,11 @@
       <c r="BZ2" s="3">
         <v>98.059026900000006</v>
       </c>
-    </row>
-    <row r="3" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA2">
+        <v>18.048340644079929</v>
+      </c>
+    </row>
+    <row r="3" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>161</v>
       </c>
@@ -4087,8 +4092,11 @@
       <c r="BZ3" s="3">
         <v>463.05255099999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA3">
+        <v>21.672332592318369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>162</v>
       </c>
@@ -4311,8 +4319,11 @@
       <c r="BZ4" s="3">
         <v>104.816551</v>
       </c>
-    </row>
-    <row r="5" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA4">
+        <v>3.4766647493357339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>163</v>
       </c>
@@ -4544,8 +4555,11 @@
       <c r="BZ5" s="3">
         <v>311.54630300000002</v>
       </c>
-    </row>
-    <row r="6" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA5">
+        <v>82.391604548617167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>362</v>
       </c>
@@ -4774,8 +4788,11 @@
       <c r="BZ6" s="3">
         <v>457.98922700000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>165</v>
       </c>
@@ -5001,8 +5018,11 @@
       <c r="BZ7" s="3">
         <v>271.50305800000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:78" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CA7">
+        <v>106.85097460792871</v>
+      </c>
+    </row>
+    <row r="8" spans="1:79" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>167</v>
       </c>
@@ -5228,8 +5248,11 @@
       <c r="BZ8" s="3">
         <v>246.10930300000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA8">
+        <v>107.7575398751739</v>
+      </c>
+    </row>
+    <row r="9" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>173</v>
       </c>
@@ -5462,8 +5485,11 @@
       <c r="BZ9" s="3">
         <v>653.34783800000002</v>
       </c>
-    </row>
-    <row r="10" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA9">
+        <v>107.6852171840538</v>
+      </c>
+    </row>
+    <row r="10" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>174</v>
       </c>
@@ -5692,8 +5718,11 @@
       <c r="BZ10" s="3">
         <v>1453.3863200000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA10">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>175</v>
       </c>
@@ -5919,8 +5948,11 @@
       <c r="BZ11" s="3">
         <v>373.78922999999998</v>
       </c>
-    </row>
-    <row r="12" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA11">
+        <v>55.327204881595151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>140</v>
       </c>
@@ -6152,8 +6184,11 @@
       <c r="BZ12" s="3">
         <v>408.006979</v>
       </c>
-    </row>
-    <row r="13" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA12">
+        <v>53.021222166223218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>141</v>
       </c>
@@ -6382,8 +6417,11 @@
       <c r="BZ13" s="3">
         <v>142.557153</v>
       </c>
-    </row>
-    <row r="14" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA13">
+        <v>45.129773985549548</v>
+      </c>
+    </row>
+    <row r="14" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>142</v>
       </c>
@@ -6609,8 +6647,11 @@
       <c r="BZ14" s="3">
         <v>130.782861</v>
       </c>
-    </row>
-    <row r="15" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA14">
+        <v>60.716825558162967</v>
+      </c>
+    </row>
+    <row r="15" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>169</v>
       </c>
@@ -6833,8 +6874,11 @@
       <c r="BZ15" s="3">
         <v>1096.3560199999999</v>
       </c>
-    </row>
-    <row r="16" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA15">
+        <v>33.914813872222197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>372</v>
       </c>
@@ -7066,8 +7110,11 @@
       <c r="BZ16" s="3">
         <v>389.85085700000002</v>
       </c>
-    </row>
-    <row r="17" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA16">
+        <v>53.823253339203767</v>
+      </c>
+    </row>
+    <row r="17" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>176</v>
       </c>
@@ -7302,8 +7349,11 @@
       <c r="BZ17" s="3">
         <v>273.40554900000001</v>
       </c>
-    </row>
-    <row r="18" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA17">
+        <v>51.611550063594287</v>
+      </c>
+    </row>
+    <row r="18" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>178</v>
       </c>
@@ -7538,8 +7588,11 @@
       <c r="BZ18" s="3">
         <v>180.67</v>
       </c>
-    </row>
-    <row r="19" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA18">
+        <v>24.651438650465241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>376</v>
       </c>
@@ -7771,8 +7824,11 @@
       <c r="BZ19" s="3">
         <v>546.34330699999998</v>
       </c>
-    </row>
-    <row r="20" spans="1:78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CA19">
+        <v>57.11847774598742</v>
+      </c>
+    </row>
+    <row r="20" spans="1:79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>183</v>
       </c>
@@ -8004,8 +8060,11 @@
       <c r="BZ20" s="3">
         <v>804.77885100000003</v>
       </c>
-    </row>
-    <row r="21" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA20">
+        <v>94.350336512207619</v>
+      </c>
+    </row>
+    <row r="21" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>184</v>
       </c>
@@ -8234,8 +8293,11 @@
       <c r="BZ21" s="3">
         <v>390.68053500000002</v>
       </c>
-    </row>
-    <row r="22" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA21">
+        <v>317.35282244174641</v>
+      </c>
+    </row>
+    <row r="22" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>186</v>
       </c>
@@ -8464,8 +8526,11 @@
       <c r="BZ22" s="3">
         <v>71.7498231</v>
       </c>
-    </row>
-    <row r="23" spans="1:78" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CA22">
+        <v>12.301495844066549</v>
+      </c>
+    </row>
+    <row r="23" spans="1:79" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>187</v>
       </c>
@@ -8697,8 +8762,11 @@
       <c r="BZ23" s="3">
         <v>1189.0187100000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA23">
+        <v>45.06621111993006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>188</v>
       </c>
@@ -8925,8 +8993,11 @@
       <c r="BZ24" s="3">
         <v>336.58480500000002</v>
       </c>
-    </row>
-    <row r="25" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA24">
+        <v>50.66522377330142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>189</v>
       </c>
@@ -9155,8 +9226,11 @@
       <c r="BZ25" s="3">
         <v>392.24178499999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA25">
+        <v>98.312820120434679</v>
+      </c>
+    </row>
+    <row r="26" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>190</v>
       </c>
@@ -9388,8 +9462,11 @@
       <c r="BZ26" s="3">
         <v>428.67800199999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA26">
+        <v>36.651664355111869</v>
+      </c>
+    </row>
+    <row r="27" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>194</v>
       </c>
@@ -9621,8 +9698,11 @@
       <c r="BZ27" s="3">
         <v>1019.07272</v>
       </c>
-    </row>
-    <row r="28" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA27">
+        <v>206.79806575513169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>193</v>
       </c>
@@ -9857,8 +9937,11 @@
       <c r="BZ28" s="3">
         <v>578.68442500000003</v>
       </c>
-    </row>
-    <row r="29" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA28">
+        <v>119.8470066377335</v>
+      </c>
+    </row>
+    <row r="29" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>199</v>
       </c>
@@ -10090,8 +10173,11 @@
       <c r="BZ29" s="3">
         <v>1282.5770299999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA29">
+        <v>112.7915998648637</v>
+      </c>
+    </row>
+    <row r="30" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>200</v>
       </c>
@@ -10321,8 +10407,11 @@
       <c r="BZ30" s="3">
         <v>106.90192399999999</v>
       </c>
-    </row>
-    <row r="31" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA30">
+        <v>26.792536274080739</v>
+      </c>
+    </row>
+    <row r="31" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>201</v>
       </c>
@@ -10545,8 +10634,11 @@
       <c r="BZ31" s="3">
         <v>488.23186900000002</v>
       </c>
-    </row>
-    <row r="32" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA31">
+        <v>300.75643102044938</v>
+      </c>
+    </row>
+    <row r="32" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>179</v>
       </c>
@@ -10778,8 +10870,11 @@
       <c r="BZ32" s="3">
         <v>752.24597300000005</v>
       </c>
-    </row>
-    <row r="33" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA32">
+        <v>56.781928008427919</v>
+      </c>
+    </row>
+    <row r="33" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>203</v>
       </c>
@@ -11011,8 +11106,11 @@
       <c r="BZ33" s="3">
         <v>284.09364099999999</v>
       </c>
-    </row>
-    <row r="34" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA33">
+        <v>149.2200204399949</v>
+      </c>
+    </row>
+    <row r="34" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>204</v>
       </c>
@@ -11241,8 +11339,11 @@
       <c r="BZ34" s="3">
         <v>207.823801</v>
       </c>
-    </row>
-    <row r="35" spans="1:78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="CA34">
+        <v>31.380728162316458</v>
+      </c>
+    </row>
+    <row r="35" spans="1:79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>205</v>
       </c>
@@ -11471,8 +11572,11 @@
       <c r="BZ35" s="3">
         <v>153.43040300000001</v>
       </c>
-    </row>
-    <row r="36" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA35">
+        <v>43.845638323730093</v>
+      </c>
+    </row>
+    <row r="36" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>208</v>
       </c>
@@ -11704,8 +11808,11 @@
       <c r="BZ36" s="3">
         <v>209.98109400000001</v>
       </c>
-    </row>
-    <row r="37" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA36">
+        <v>19.411231737330901</v>
+      </c>
+    </row>
+    <row r="37" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>209</v>
       </c>
@@ -11934,8 +12041,11 @@
       <c r="BZ37" s="3">
         <v>337.576437</v>
       </c>
-    </row>
-    <row r="38" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA37">
+        <v>62.782481632979582</v>
+      </c>
+    </row>
+    <row r="38" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>298</v>
       </c>
@@ -12164,8 +12274,11 @@
       <c r="BZ38" s="3">
         <v>1147.6425200000001</v>
       </c>
-    </row>
-    <row r="39" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA38">
+        <v>221.43855716655179</v>
+      </c>
+    </row>
+    <row r="39" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>210</v>
       </c>
@@ -12394,8 +12507,11 @@
       <c r="BZ39" s="3">
         <v>831.54528700000003</v>
       </c>
-    </row>
-    <row r="40" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA39">
+        <v>24.690095180185772</v>
+      </c>
+    </row>
+    <row r="40" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>145</v>
       </c>
@@ -12624,8 +12740,11 @@
       <c r="BZ40" s="3">
         <v>169.20834099999999</v>
       </c>
-    </row>
-    <row r="41" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA40">
+        <v>35.508855233332987</v>
+      </c>
+    </row>
+    <row r="41" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>146</v>
       </c>
@@ -12854,8 +12973,11 @@
       <c r="BZ41" s="3">
         <v>99.488946600000006</v>
       </c>
-    </row>
-    <row r="42" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA41">
+        <v>20.798136935756801</v>
+      </c>
+    </row>
+    <row r="42" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>147</v>
       </c>
@@ -13084,8 +13206,11 @@
       <c r="BZ42" s="3">
         <v>145.11185900000001</v>
       </c>
-    </row>
-    <row r="43" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA42">
+        <v>40.561972338910778</v>
+      </c>
+    </row>
+    <row r="43" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>211</v>
       </c>
@@ -13314,8 +13439,11 @@
       <c r="BZ43" s="3">
         <v>395.18027799999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA43">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>148</v>
       </c>
@@ -13547,8 +13675,11 @@
       <c r="BZ44" s="3">
         <v>1203.42147</v>
       </c>
-    </row>
-    <row r="45" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA44">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>170</v>
       </c>
@@ -13780,8 +13911,11 @@
       <c r="BZ45" s="3">
         <v>311.41606000000002</v>
       </c>
-    </row>
-    <row r="46" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA45">
+        <v>105.3652167462092</v>
+      </c>
+    </row>
+    <row r="46" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>151</v>
       </c>
@@ -14013,8 +14147,11 @@
       <c r="BZ46" s="3">
         <v>371.22063200000002</v>
       </c>
-    </row>
-    <row r="47" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA46">
+        <v>39.99577645342967</v>
+      </c>
+    </row>
+    <row r="47" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>152</v>
       </c>
@@ -14240,8 +14377,11 @@
       <c r="BZ47" s="3">
         <v>81.654024399999997</v>
       </c>
-    </row>
-    <row r="48" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA47">
+        <v>9.4247622100204023</v>
+      </c>
+    </row>
+    <row r="48" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>154</v>
       </c>
@@ -14467,8 +14607,11 @@
       <c r="BZ48" s="3">
         <v>176.71025599999999</v>
       </c>
-    </row>
-    <row r="49" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA48">
+        <v>11.02190954234066</v>
+      </c>
+    </row>
+    <row r="49" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>155</v>
       </c>
@@ -14697,8 +14840,11 @@
       <c r="BZ49" s="3">
         <v>66.528607600000001</v>
       </c>
-    </row>
-    <row r="50" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA49">
+        <v>27.262459536960069</v>
+      </c>
+    </row>
+    <row r="50" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>156</v>
       </c>
@@ -14930,8 +15076,11 @@
       <c r="BZ50" s="3">
         <v>211.47773599999999</v>
       </c>
-    </row>
-    <row r="51" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA50">
+        <v>11.377613985757449</v>
+      </c>
+    </row>
+    <row r="51" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>158</v>
       </c>
@@ -15160,8 +15309,11 @@
       <c r="BZ51" s="3">
         <v>146.174194</v>
       </c>
-    </row>
-    <row r="52" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA51">
+        <v>52.481629230034507</v>
+      </c>
+    </row>
+    <row r="52" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>208</v>
       </c>
@@ -15393,8 +15545,11 @@
       <c r="BZ52" s="3">
         <v>209.98109438004749</v>
       </c>
-    </row>
-    <row r="53" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA52">
+        <v>19.411231737330901</v>
+      </c>
+    </row>
+    <row r="53" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>209</v>
       </c>
@@ -15623,8 +15778,11 @@
       <c r="BZ53" s="3">
         <v>337.57643664787253</v>
       </c>
-    </row>
-    <row r="54" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA53">
+        <v>62.782481632979582</v>
+      </c>
+    </row>
+    <row r="54" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>298</v>
       </c>
@@ -15853,8 +16011,11 @@
       <c r="BZ54" s="3">
         <v>1147.642516301963</v>
       </c>
-    </row>
-    <row r="55" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA54">
+        <v>221.43855716655179</v>
+      </c>
+    </row>
+    <row r="55" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>210</v>
       </c>
@@ -16083,8 +16244,11 @@
       <c r="BZ55" s="3">
         <v>831.54528720477924</v>
       </c>
-    </row>
-    <row r="56" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="CA55">
+        <v>24.690095180185772</v>
+      </c>
+    </row>
+    <row r="56" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>211</v>
       </c>
@@ -16312,6 +16476,9 @@
       </c>
       <c r="BZ56" s="3">
         <v>395.18027778863848</v>
+      </c>
+      <c r="CA56">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/prairies/data/Releves_prairies_biomasse_et_phyto.xlsx
+++ b/prairies/data/Releves_prairies_biomasse_et_phyto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ingé\3A\Stage\Cervides_Aubrac\Analyse\Analyses_Aubrac\prairies\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B2B63C-A404-494F-BC20-94DFE02CC412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8504A7-1177-434D-AA4D-F9E482A1B700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10679,7 +10679,7 @@
         <v>81</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O32" s="7" t="s">
         <v>81</v>
@@ -12782,7 +12782,7 @@
         <v>81</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O41" s="7" t="s">
         <v>81</v>
